--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F7ECC9-C5C8-4F70-A0B7-52664A63A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1D85D-3A41-41CD-823D-1FE80A95939F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="457">
   <si>
     <t>Id</t>
   </si>
@@ -655,780 +655,896 @@
     <t>W111</t>
   </si>
   <si>
+    <t>[6,3,6]</t>
+  </si>
+  <si>
+    <t>[Damage_Madness,Damage,Damage_Peace]</t>
+  </si>
+  <si>
+    <t>智者的悲叹</t>
+  </si>
+  <si>
+    <t>W112</t>
+  </si>
+  <si>
+    <t>OceanElementBottle</t>
+  </si>
+  <si>
+    <t>[Heal,Draw,Discard]</t>
+  </si>
+  <si>
+    <t>海洋元素瓶</t>
+  </si>
+  <si>
+    <t>W113</t>
+  </si>
+  <si>
+    <t>EndlessWave</t>
+  </si>
+  <si>
+    <t>[8,1,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Madness,Discard_Madness,Draw]</t>
+  </si>
+  <si>
+    <t>不休的浪潮</t>
+  </si>
+  <si>
+    <t>W201</t>
+  </si>
+  <si>
+    <t>GreaterWaterPotion</t>
+  </si>
+  <si>
+    <t>[9,1,7]</t>
+  </si>
+  <si>
+    <t>高等水流药剂</t>
+  </si>
+  <si>
+    <t>W202</t>
+  </si>
+  <si>
+    <t>LionsTears</t>
+  </si>
+  <si>
+    <t>[1,0,0]</t>
+  </si>
+  <si>
+    <t>[LED_Water,Damage,Heal]</t>
+  </si>
+  <si>
+    <t>狮子的眼泪</t>
+  </si>
+  <si>
+    <t>W203</t>
+  </si>
+  <si>
+    <t>ForbiddenDroplet</t>
+  </si>
+  <si>
+    <t>[1,4,1]</t>
+  </si>
+  <si>
+    <t>[Discard,Neutralize,Draw_Peace]</t>
+  </si>
+  <si>
+    <t>禁忌的一滴</t>
+  </si>
+  <si>
+    <t>W204</t>
+  </si>
+  <si>
+    <t>BottledSwirl</t>
+  </si>
+  <si>
+    <t>[6,2,1]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Stun_Enemy,Buff_Stun_Enemy_Madness]</t>
+  </si>
+  <si>
+    <t>瓶装漩涡</t>
+  </si>
+  <si>
+    <t>W205</t>
+  </si>
+  <si>
+    <t>BottledOasis</t>
+  </si>
+  <si>
+    <t>[5,1,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Peace,Draw_Peace,Quickness_Peace]</t>
+  </si>
+  <si>
+    <t>瓶装绿洲</t>
+  </si>
+  <si>
+    <t>W206</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
+  </si>
+  <si>
+    <t>[0,3,0,0]</t>
+  </si>
+  <si>
+    <t>[8,3,6]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Stun_Enemy,Discard]</t>
+  </si>
+  <si>
+    <t>海啸</t>
+  </si>
+  <si>
+    <t>W207</t>
+  </si>
+  <si>
+    <t>ConstantFlux</t>
+  </si>
+  <si>
+    <t>[5,5,5]</t>
+  </si>
+  <si>
+    <t>[Heal_Madness,Discard_Madness,Draw_Madness]</t>
+  </si>
+  <si>
+    <t>流转的呼吸</t>
+  </si>
+  <si>
+    <t>FW100</t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>Fire_Water</t>
+  </si>
+  <si>
+    <t>[1,1,0,0]</t>
+  </si>
+  <si>
+    <t>[1,1,0]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Burn_Self,Heal]</t>
+  </si>
+  <si>
+    <t>乙醇</t>
+  </si>
+  <si>
+    <t>FW101</t>
+  </si>
+  <si>
+    <t>Lorazepam</t>
+  </si>
+  <si>
+    <t>[true,true,false,false]</t>
+  </si>
+  <si>
+    <t>[3,2,4]</t>
+  </si>
+  <si>
+    <t>[Buff_Calm_Self,Draw,Heal]</t>
+  </si>
+  <si>
+    <t>劳拉西泮</t>
+  </si>
+  <si>
+    <t>FW102</t>
+  </si>
+  <si>
+    <t>DryIce</t>
+  </si>
+  <si>
+    <t>[5,4,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Cooldown,Damage,Buff_Quickness_Self]</t>
+  </si>
+  <si>
+    <t>干冰</t>
+  </si>
+  <si>
+    <t>FW103</t>
+  </si>
+  <si>
+    <t>ConcentratedNitricAcid</t>
+  </si>
+  <si>
+    <t>[5,3,4]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Damage]</t>
+  </si>
+  <si>
+    <t>浓硝酸</t>
+  </si>
+  <si>
+    <t>FW104</t>
+  </si>
+  <si>
+    <t>Ammonia</t>
+  </si>
+  <si>
+    <t>[Damage_Cooldown,Draw,Damage]</t>
+  </si>
+  <si>
+    <t>液态氨</t>
+  </si>
+  <si>
+    <t>FW105</t>
+  </si>
+  <si>
+    <t>Dopamine</t>
+  </si>
+  <si>
+    <t>[4,1,4]</t>
+  </si>
+  <si>
+    <t>[Quickness_Peace,Buff_Burn_Self,Heal_Madness]</t>
+  </si>
+  <si>
+    <t>多巴胺</t>
+  </si>
+  <si>
+    <t>FW106</t>
+  </si>
+  <si>
+    <t>Methane</t>
+  </si>
+  <si>
+    <t>[3,9,3]</t>
+  </si>
+  <si>
+    <t>[Draw_Unstable,Damage_Cooldown,Buff_Burn_Self]</t>
+  </si>
+  <si>
+    <t>甲烷</t>
+  </si>
+  <si>
+    <t>FW201</t>
+  </si>
+  <si>
+    <t>SodiumBicarbonate</t>
+  </si>
+  <si>
+    <t>[3,3,5]</t>
+  </si>
+  <si>
+    <t>[Draw_Cooldown,Neutralize,Heal]</t>
+  </si>
+  <si>
+    <t>碳酸氢钠</t>
+  </si>
+  <si>
+    <t>FW202</t>
+  </si>
+  <si>
+    <t>Trinitrotoluene</t>
+  </si>
+  <si>
+    <t>[4,10,1]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Self,Damage,Elemental_Water]</t>
+  </si>
+  <si>
+    <t>三硝基甲苯</t>
+  </si>
+  <si>
+    <t>FW203</t>
+  </si>
+  <si>
+    <t>Graphene</t>
+  </si>
+  <si>
+    <t>[2,1,0,0]</t>
+  </si>
+  <si>
+    <t>[8,1,4]</t>
+  </si>
+  <si>
+    <t>[Ignite_Cooldown,Elemental_Water_Madness,Damage]</t>
+  </si>
+  <si>
+    <t>石墨烯</t>
+  </si>
+  <si>
+    <t>FW204</t>
+  </si>
+  <si>
+    <t>TaqDNAPolymerase</t>
+  </si>
+  <si>
+    <t>[2,2,5]</t>
+  </si>
+  <si>
+    <t>[Draw_Cooldown,Catalyze,Catalyze]</t>
+  </si>
+  <si>
+    <t>Taq酶</t>
+  </si>
+  <si>
+    <t>FW205</t>
+  </si>
+  <si>
+    <t>Chloroform</t>
+  </si>
+  <si>
+    <t>[1,1,5]</t>
+  </si>
+  <si>
+    <t>[Elemental_Water,Elemental_Fire,Damage_Self]</t>
+  </si>
+  <si>
+    <t>氯仿</t>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch_Test1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>Branch_Test2</t>
+  </si>
+  <si>
+    <t>InternalBurningPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnstableFirePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmberPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExternalBurningPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFireball</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledPhoenix</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSimianSpirit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FireElementBottle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BasicFirePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FirePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.PowerPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.HeatTherapy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.CatalyzePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.ScalePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FlashPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.WillOWisp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BlastPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.InternalBurningPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.UnstableFirePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.EmberPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.ExternalBurningPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.GreaterFirePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.PulsePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.SuperNova</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.MidasPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledFireball</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledPhoenix</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledSimianSpirit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.WaterElementBottle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicWaterPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.BasicWaterPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.WaterPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.SpeedPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthElementBottle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Test</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false,true,false]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>土元素瓶</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础大地药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E101</t>
+  </si>
+  <si>
+    <t>E102</t>
+  </si>
+  <si>
+    <t>E103</t>
+  </si>
+  <si>
+    <t>E104</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E105</t>
+  </si>
+  <si>
+    <t>E106</t>
+  </si>
+  <si>
+    <t>E107</t>
+  </si>
+  <si>
+    <t>E108</t>
+  </si>
+  <si>
+    <t>E109</t>
+  </si>
+  <si>
+    <t>E110</t>
+  </si>
+  <si>
+    <t>E111</t>
+  </si>
+  <si>
+    <t>E112</t>
+  </si>
+  <si>
+    <t>E113</t>
+  </si>
+  <si>
+    <t>E201</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E202</t>
+  </si>
+  <si>
+    <t>E203</t>
+  </si>
+  <si>
+    <t>E204</t>
+  </si>
+  <si>
+    <t>E205</t>
+  </si>
+  <si>
+    <t>E206</t>
+  </si>
+  <si>
+    <t>E207</t>
+  </si>
+  <si>
+    <t>BasicEarthPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,3,2]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地核药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthCorePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,3,3]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定占位</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.HealPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeutralizePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.NeutralizePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CyclePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalmMindPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.CalmMindPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>LamentOfTheWise</t>
-  </si>
-  <si>
-    <t>[6,3,6]</t>
-  </si>
-  <si>
-    <t>[Damage_Madness,Damage,Damage_Peace]</t>
-  </si>
-  <si>
-    <t>智者的悲叹</t>
-  </si>
-  <si>
-    <t>W112</t>
-  </si>
-  <si>
-    <t>OceanElementBottle</t>
-  </si>
-  <si>
-    <t>[Heal,Draw,Discard]</t>
-  </si>
-  <si>
-    <t>海洋元素瓶</t>
-  </si>
-  <si>
-    <t>W113</t>
-  </si>
-  <si>
-    <t>EndlessWave</t>
-  </si>
-  <si>
-    <t>[8,1,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Madness,Discard_Madness,Draw]</t>
-  </si>
-  <si>
-    <t>不休的浪潮</t>
-  </si>
-  <si>
-    <t>W201</t>
-  </si>
-  <si>
-    <t>GreaterWaterPotion</t>
-  </si>
-  <si>
-    <t>[9,1,7]</t>
-  </si>
-  <si>
-    <t>高等水流药剂</t>
-  </si>
-  <si>
-    <t>W202</t>
-  </si>
-  <si>
-    <t>LionsTears</t>
-  </si>
-  <si>
-    <t>[1,0,0]</t>
-  </si>
-  <si>
-    <t>[LED_Water,Damage,Heal]</t>
-  </si>
-  <si>
-    <t>狮子的眼泪</t>
-  </si>
-  <si>
-    <t>W203</t>
-  </si>
-  <si>
-    <t>ForbiddenDroplet</t>
-  </si>
-  <si>
-    <t>[1,4,1]</t>
-  </si>
-  <si>
-    <t>[Discard,Neutralize,Draw_Peace]</t>
-  </si>
-  <si>
-    <t>禁忌的一滴</t>
-  </si>
-  <si>
-    <t>W204</t>
-  </si>
-  <si>
-    <t>BottledSwirl</t>
-  </si>
-  <si>
-    <t>[6,2,1]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Stun_Enemy,Buff_Stun_Enemy_Madness]</t>
-  </si>
-  <si>
-    <t>瓶装漩涡</t>
-  </si>
-  <si>
-    <t>W205</t>
-  </si>
-  <si>
-    <t>BottledOasis</t>
-  </si>
-  <si>
-    <t>[5,1,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Peace,Draw_Peace,Quickness_Peace]</t>
-  </si>
-  <si>
-    <t>瓶装绿洲</t>
-  </si>
-  <si>
-    <t>W206</t>
-  </si>
-  <si>
-    <t>Tsunami</t>
-  </si>
-  <si>
-    <t>[0,3,0,0]</t>
-  </si>
-  <si>
-    <t>[8,3,6]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Stun_Enemy,Discard]</t>
-  </si>
-  <si>
-    <t>海啸</t>
-  </si>
-  <si>
-    <t>W207</t>
-  </si>
-  <si>
-    <t>ConstantFlux</t>
-  </si>
-  <si>
-    <t>[5,5,5]</t>
-  </si>
-  <si>
-    <t>[Heal_Madness,Discard_Madness,Draw_Madness]</t>
-  </si>
-  <si>
-    <t>流转的呼吸</t>
-  </si>
-  <si>
-    <t>FW100</t>
-  </si>
-  <si>
-    <t>Ethanol</t>
-  </si>
-  <si>
-    <t>Fire_Water</t>
-  </si>
-  <si>
-    <t>[1,1,0,0]</t>
-  </si>
-  <si>
-    <t>[1,1,0]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Burn_Self,Heal]</t>
-  </si>
-  <si>
-    <t>乙醇</t>
-  </si>
-  <si>
-    <t>FW101</t>
-  </si>
-  <si>
-    <t>Lorazepam</t>
-  </si>
-  <si>
-    <t>[true,true,false,false]</t>
-  </si>
-  <si>
-    <t>[3,2,4]</t>
-  </si>
-  <si>
-    <t>[Buff_Calm_Self,Draw,Heal]</t>
-  </si>
-  <si>
-    <t>劳拉西泮</t>
-  </si>
-  <si>
-    <t>FW102</t>
-  </si>
-  <si>
-    <t>DryIce</t>
-  </si>
-  <si>
-    <t>[5,4,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Cooldown,Damage,Buff_Quickness_Self]</t>
-  </si>
-  <si>
-    <t>干冰</t>
-  </si>
-  <si>
-    <t>FW103</t>
-  </si>
-  <si>
-    <t>ConcentratedNitricAcid</t>
-  </si>
-  <si>
-    <t>[5,3,4]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Damage]</t>
-  </si>
-  <si>
-    <t>浓硝酸</t>
-  </si>
-  <si>
-    <t>FW104</t>
-  </si>
-  <si>
-    <t>Ammonia</t>
-  </si>
-  <si>
-    <t>[Damage_Cooldown,Draw,Damage]</t>
-  </si>
-  <si>
-    <t>液态氨</t>
-  </si>
-  <si>
-    <t>FW105</t>
-  </si>
-  <si>
-    <t>Dopamine</t>
-  </si>
-  <si>
-    <t>[4,1,4]</t>
-  </si>
-  <si>
-    <t>[Quickness_Peace,Buff_Burn_Self,Heal_Madness]</t>
-  </si>
-  <si>
-    <t>多巴胺</t>
-  </si>
-  <si>
-    <t>FW106</t>
-  </si>
-  <si>
-    <t>Methane</t>
-  </si>
-  <si>
-    <t>[3,9,3]</t>
-  </si>
-  <si>
-    <t>[Draw_Unstable,Damage_Cooldown,Buff_Burn_Self]</t>
-  </si>
-  <si>
-    <t>甲烷</t>
-  </si>
-  <si>
-    <t>FW201</t>
-  </si>
-  <si>
-    <t>SodiumBicarbonate</t>
-  </si>
-  <si>
-    <t>[3,3,5]</t>
-  </si>
-  <si>
-    <t>[Draw_Cooldown,Neutralize,Heal]</t>
-  </si>
-  <si>
-    <t>碳酸氢钠</t>
-  </si>
-  <si>
-    <t>FW202</t>
-  </si>
-  <si>
-    <t>Trinitrotoluene</t>
-  </si>
-  <si>
-    <t>[4,10,1]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Self,Damage,Elemental_Water]</t>
-  </si>
-  <si>
-    <t>三硝基甲苯</t>
-  </si>
-  <si>
-    <t>FW203</t>
-  </si>
-  <si>
-    <t>Graphene</t>
-  </si>
-  <si>
-    <t>[2,1,0,0]</t>
-  </si>
-  <si>
-    <t>[8,1,4]</t>
-  </si>
-  <si>
-    <t>[Ignite_Cooldown,Elemental_Water_Madness,Damage]</t>
-  </si>
-  <si>
-    <t>石墨烯</t>
-  </si>
-  <si>
-    <t>FW204</t>
-  </si>
-  <si>
-    <t>TaqDNAPolymerase</t>
-  </si>
-  <si>
-    <t>[2,2,5]</t>
-  </si>
-  <si>
-    <t>[Draw_Cooldown,Catalyze,Catalyze]</t>
-  </si>
-  <si>
-    <t>Taq酶</t>
-  </si>
-  <si>
-    <t>FW205</t>
-  </si>
-  <si>
-    <t>Chloroform</t>
-  </si>
-  <si>
-    <t>[1,1,5]</t>
-  </si>
-  <si>
-    <t>[Elemental_Water,Elemental_Fire,Damage_Self]</t>
-  </si>
-  <si>
-    <t>氯仿</t>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>B01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch_Test1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>B02</t>
-  </si>
-  <si>
-    <t>Branch_Test2</t>
-  </si>
-  <si>
-    <t>InternalBurningPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnstableFirePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmberPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledFireball</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledPhoenix</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicWaterPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthElementBottle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Test</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[false,false,true,false]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>土元素瓶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础大地药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E101</t>
-  </si>
-  <si>
-    <t>E102</t>
-  </si>
-  <si>
-    <t>E103</t>
-  </si>
-  <si>
-    <t>E104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E105</t>
-  </si>
-  <si>
-    <t>E106</t>
-  </si>
-  <si>
-    <t>E107</t>
-  </si>
-  <si>
-    <t>E108</t>
-  </si>
-  <si>
-    <t>E109</t>
-  </si>
-  <si>
-    <t>E110</t>
-  </si>
-  <si>
-    <t>E111</t>
-  </si>
-  <si>
-    <t>E112</t>
-  </si>
-  <si>
-    <t>E113</t>
-  </si>
-  <si>
-    <t>E201</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E202</t>
-  </si>
-  <si>
-    <t>E203</t>
-  </si>
-  <si>
-    <t>E204</t>
-  </si>
-  <si>
-    <t>E205</t>
-  </si>
-  <si>
-    <t>E206</t>
-  </si>
-  <si>
-    <t>E207</t>
-  </si>
-  <si>
-    <t>BasicEarthPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,3,2]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>地核药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthCorePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,3,3]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>待定占位</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeutralizePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CyclePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalmMindPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LamentOfTheWise</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,1,0]</t>
   </si>
   <si>
     <t>[0,0,1,0]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>健体药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[5,1,1]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[7,5,1]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,1]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[12,2,1]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,2,0]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,3,0]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,1]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>[14,10,9]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FocusPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Draw_Focus]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,8,0]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Reflect_Self,Draw,Damage]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpikePotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,1,1]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地壳药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrustPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,3,1]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地能药剂</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPowerPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Draw,Discard]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[9,2,1]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>息壤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,0]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,0,3]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfEarth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野之息</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfTheWild</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoarOfTheEarth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>土石咆哮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Damage_Focus]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,5,6]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1506,23 +1622,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,20 +1917,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.09765625" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="5" max="5" width="22.19921875" customWidth="1"/>
+    <col min="6" max="6" width="22.3984375" customWidth="1"/>
+    <col min="7" max="7" width="19.09765625" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="62.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.09765625" customWidth="1"/>
+    <col min="11" max="11" width="62.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1847,7 +1965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1882,7 +2000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1917,7 +2035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1937,7 +2055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1972,7 +2090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1980,7 +2098,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E6" t="s">
         <v>39</v>
@@ -2004,7 +2122,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2036,12 +2154,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -2068,12 +2186,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -2101,7 +2219,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2109,19 +2227,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2156,7 +2274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,7 +2282,7 @@
         <v>57</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -2191,7 +2309,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>60</v>
       </c>
@@ -2199,7 +2317,7 @@
         <v>61</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2208,7 +2326,7 @@
         <v>33</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>58</v>
@@ -2226,7 +2344,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -2234,7 +2352,7 @@
         <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>39</v>
@@ -2261,7 +2379,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -2269,7 +2387,7 @@
         <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
@@ -2296,7 +2414,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
@@ -2304,7 +2422,7 @@
         <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>39</v>
@@ -2331,7 +2449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -2339,7 +2457,7 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>39</v>
@@ -2366,7 +2484,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>85</v>
       </c>
@@ -2374,7 +2492,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
@@ -2401,7 +2519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>90</v>
       </c>
@@ -2409,7 +2527,7 @@
         <v>91</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -2436,7 +2554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>95</v>
       </c>
@@ -2444,7 +2562,7 @@
         <v>96</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>39</v>
@@ -2471,7 +2589,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
@@ -2479,7 +2597,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>39</v>
@@ -2506,15 +2624,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>39</v>
@@ -2541,15 +2659,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>39</v>
@@ -2576,15 +2694,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>39</v>
@@ -2611,15 +2729,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>39</v>
@@ -2646,7 +2764,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -2654,7 +2772,7 @@
         <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>39</v>
@@ -2681,7 +2799,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>127</v>
       </c>
@@ -2689,7 +2807,7 @@
         <v>128</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>39</v>
@@ -2698,7 +2816,7 @@
         <v>67</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>58</v>
@@ -2716,7 +2834,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>132</v>
       </c>
@@ -2724,7 +2842,7 @@
         <v>133</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>39</v>
@@ -2751,7 +2869,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>138</v>
       </c>
@@ -2759,7 +2877,7 @@
         <v>139</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>39</v>
@@ -2786,15 +2904,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>39</v>
@@ -2821,15 +2939,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>39</v>
@@ -2856,15 +2974,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>39</v>
@@ -2892,7 +3010,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2900,20 +3018,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2948,7 +3066,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>155</v>
       </c>
@@ -2956,7 +3074,7 @@
         <v>156</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>51</v>
@@ -2983,15 +3101,15 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>353</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>51</v>
@@ -3018,7 +3136,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>163</v>
       </c>
@@ -3026,7 +3144,7 @@
         <v>164</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>51</v>
@@ -3053,7 +3171,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>169</v>
       </c>
@@ -3061,7 +3179,7 @@
         <v>170</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>51</v>
@@ -3088,15 +3206,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
@@ -3123,15 +3241,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>395</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>396</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>51</v>
@@ -3158,15 +3276,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>51</v>
@@ -3193,15 +3311,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>398</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>399</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>51</v>
@@ -3228,7 +3346,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>189</v>
       </c>
@@ -3236,7 +3354,7 @@
         <v>190</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>51</v>
@@ -3263,7 +3381,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>195</v>
       </c>
@@ -3271,7 +3389,7 @@
         <v>196</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>51</v>
@@ -3298,7 +3416,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>200</v>
       </c>
@@ -3306,7 +3424,7 @@
         <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>51</v>
@@ -3333,15 +3451,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>400</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>401</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>51</v>
@@ -3359,24 +3477,24 @@
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="L14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>211</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>51</v>
@@ -3397,21 +3515,21 @@
         <v>34</v>
       </c>
       <c r="K15" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="L15" s="5" t="s">
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>51</v>
@@ -3429,21 +3547,21 @@
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L16" s="5" t="s">
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
@@ -3464,21 +3582,21 @@
         <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>167</v>
       </c>
       <c r="L18" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
@@ -3499,21 +3617,21 @@
         <v>8</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
@@ -3534,21 +3652,21 @@
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="L20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -3569,21 +3687,21 @@
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="L21" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="L21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -3604,21 +3722,21 @@
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="L22" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="L22" s="6" t="s">
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -3633,27 +3751,27 @@
         <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I23" s="3">
         <v>9</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K23" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="L23" s="6" t="s">
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -3674,26 +3792,26 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3701,20 +3819,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2441ED13-5DB1-49F6-B610-4785970FA9EB}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3749,18 +3867,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -3769,7 +3887,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -3778,24 +3896,24 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -3804,182 +3922,182 @@
         <v>46</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>359</v>
-      </c>
       <c r="G4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>359</v>
-      </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K7" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -3988,374 +4106,374 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>421</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
-      <c r="A11" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>422</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>359</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>196</v>
+        <v>371</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>430</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>402</v>
+      <c r="H12" s="16" t="s">
+        <v>425</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>198</v>
+      <c r="J12" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>431</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>201</v>
+        <v>372</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>435</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>202</v>
+        <v>436</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>203</v>
+        <v>433</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>206</v>
+        <v>373</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>442</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>402</v>
+      <c r="H14" s="16" t="s">
+        <v>425</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+      <c r="J14" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>211</v>
+        <v>374</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>438</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>34</v>
+        <v>444</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>212</v>
+        <v>443</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>215</v>
+        <v>449</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>403</v>
+      <c r="H16" s="16" t="s">
+        <v>446</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>216</v>
+        <v>448</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>217</v>
+        <v>447</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>359</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>224</v>
+        <v>377</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>451</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>403</v>
+      <c r="H19" s="17" t="s">
+        <v>446</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>226</v>
+      <c r="J19" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>452</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>229</v>
+        <v>378</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>453</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>402</v>
+      <c r="H20" s="17" t="s">
+        <v>425</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>231</v>
+      <c r="J20" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>455</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -4364,33 +4482,33 @@
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="6" t="s">
-        <v>236</v>
-      </c>
       <c r="L21" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
@@ -4399,33 +4517,33 @@
         <v>40</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>241</v>
-      </c>
       <c r="L22" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -4434,33 +4552,33 @@
         <v>40</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K23" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>247</v>
-      </c>
       <c r="L23" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>33</v>
@@ -4469,32 +4587,32 @@
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="L24" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4502,19 +4620,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4549,18 +4667,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -4569,27 +4687,27 @@
         <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I2" s="1">
         <v>4</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="L2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>32</v>
@@ -4598,7 +4716,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>46</v>
@@ -4610,21 +4728,21 @@
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="L4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -4633,7 +4751,7 @@
         <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>46</v>
@@ -4645,91 +4763,91 @@
         <v>4</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="L5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="I6" s="2">
         <v>4</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="L6" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="L6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="I7" s="2">
         <v>6</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="L7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -4738,7 +4856,7 @@
         <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
@@ -4750,21 +4868,21 @@
         <v>6</v>
       </c>
       <c r="J8" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="L8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
@@ -4773,7 +4891,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
@@ -4785,21 +4903,21 @@
         <v>5</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="L9" s="5" t="s">
+    </row>
+    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" s="3" customFormat="1">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>32</v>
@@ -4808,7 +4926,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>40</v>
@@ -4820,21 +4938,21 @@
         <v>7</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="L11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" s="3" customFormat="1">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>32</v>
@@ -4843,7 +4961,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>40</v>
@@ -4855,65 +4973,65 @@
         <v>7</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="L12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" s="3" customFormat="1">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I13" s="3">
         <v>8</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="L13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" s="3" customFormat="1">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>40</v>
@@ -4925,52 +5043,52 @@
         <v>7</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="L14" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="L14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" s="3" customFormat="1">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>313</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I15" s="3">
         <v>10</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="L15" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>316</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1D85D-3A41-41CD-823D-1FE80A95939F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0E7E2A-A759-4916-8BBB-BC4940D54F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -1643,7 +1643,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1919,15 +1919,15 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.09765625" customWidth="1"/>
-    <col min="2" max="2" width="19.3984375" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="5" max="5" width="22.19921875" customWidth="1"/>
-    <col min="6" max="6" width="22.3984375" customWidth="1"/>
-    <col min="7" max="7" width="19.09765625" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="10" max="10" width="14.09765625" customWidth="1"/>
-    <col min="11" max="11" width="62.796875" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="62.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2229,14 +2229,14 @@
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3020,15 +3020,15 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="3" width="28.296875" customWidth="1"/>
-    <col min="4" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3821,15 +3821,15 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="3" width="28.296875" customWidth="1"/>
-    <col min="4" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4622,14 +4622,14 @@
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0E7E2A-A759-4916-8BBB-BC4940D54F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E945AC-D993-4317-A55E-6382BB04D2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
     <sheet name="Fire" sheetId="2" r:id="rId2"/>
     <sheet name="Water" sheetId="3" r:id="rId3"/>
     <sheet name="Earth" sheetId="6" r:id="rId4"/>
-    <sheet name="Fire_Water" sheetId="4" r:id="rId5"/>
+    <sheet name="Air" sheetId="8" r:id="rId5"/>
+    <sheet name="Fire_Water" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="481">
   <si>
     <t>Id</t>
   </si>
@@ -986,19 +987,19 @@
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>B01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>B02</t>
@@ -1008,167 +1009,167 @@
   </si>
   <si>
     <t>InternalBurningPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>UnstableFirePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EmberPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BottledFireball</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BottledPhoenix</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BasicWaterPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Test</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Earth</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,true,false]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>E100</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>E101</t>
@@ -1181,7 +1182,7 @@
   </si>
   <si>
     <t>E104</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>E105</t>
@@ -1212,7 +1213,7 @@
   </si>
   <si>
     <t>E201</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>E202</t>
@@ -1234,310 +1235,395 @@
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,2]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,3]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>待定占位</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>HealPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>NeutralizePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CyclePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CalmMindPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>LamentOfTheWise</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,1,0]</t>
   </si>
   <si>
     <t>[0,0,1,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>健体药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[5,1,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[7,5,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[12,2,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,2,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,3,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[14,10,9]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Draw_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[5,8,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Reflect_Self,Draw,Damage]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[6,1,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Draw,Discard]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[9,2,1]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[3,0,3]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>[6,5,6]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A100</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>A104</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>A106</t>
+  </si>
+  <si>
+    <t>A107</t>
+  </si>
+  <si>
+    <t>A108</t>
+  </si>
+  <si>
+    <t>A109</t>
+  </si>
+  <si>
+    <t>A110</t>
+  </si>
+  <si>
+    <t>A111</t>
+  </si>
+  <si>
+    <t>A112</t>
+  </si>
+  <si>
+    <t>A113</t>
+  </si>
+  <si>
+    <t>A201</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>A203</t>
+  </si>
+  <si>
+    <t>A204</t>
+  </si>
+  <si>
+    <t>A205</t>
+  </si>
+  <si>
+    <t>A206</t>
+  </si>
+  <si>
+    <t>A207</t>
+  </si>
+  <si>
+    <t>Air</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false,false,true]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,1]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1583,6 +1669,11 @@
       <name val="等线"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1622,25 +1713,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2219,7 +2311,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3010,7 +3102,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3811,7 +3903,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4612,12 +4704,813 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C02A9BF-5C11-492C-BF77-FB0B6AF52D8A}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="I10" s="2">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="I18" s="3">
+        <v>8</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="I19" s="3">
+        <v>8</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="I20" s="3">
+        <v>8</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="I21" s="3">
+        <v>8</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="I22" s="3">
+        <v>8</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="I23" s="3">
+        <v>8</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="I24" s="3">
+        <v>8</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K28" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -5088,7 +5981,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E945AC-D993-4317-A55E-6382BB04D2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328DAE95-1F2E-4978-8011-C005C1BE38FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="514">
   <si>
     <t>Id</t>
   </si>
@@ -987,19 +987,19 @@
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>B01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>B02</t>
@@ -1009,167 +1009,167 @@
   </si>
   <si>
     <t>InternalBurningPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>UnstableFirePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EmberPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BottledFireball</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BottledPhoenix</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BasicWaterPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Test</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Earth</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,true,false]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>E100</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>E101</t>
@@ -1182,7 +1182,7 @@
   </si>
   <si>
     <t>E104</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>E105</t>
@@ -1213,7 +1213,7 @@
   </si>
   <si>
     <t>E201</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>E202</t>
@@ -1235,302 +1235,302 @@
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,2]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,3]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>待定占位</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>HealPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>NeutralizePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CyclePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CalmMindPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>LamentOfTheWise</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,1,0]</t>
   </si>
   <si>
     <t>[0,0,1,0]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>健体药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[5,1,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[7,5,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[12,2,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,2,0]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,3,0]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[14,10,9]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Draw_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[5,8,0]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Reflect_Self,Draw,Damage]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[6,1,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Draw,Discard]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[9,2,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,0]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[3,0,3]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[6,5,6]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>A100</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>A101</t>
@@ -1543,7 +1543,7 @@
   </si>
   <si>
     <t>A104</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>A105</t>
@@ -1574,7 +1574,7 @@
   </si>
   <si>
     <t>A201</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>A202</t>
@@ -1596,27 +1596,173 @@
   </si>
   <si>
     <t>Air</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,false,true]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,1]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirElementBottle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>气元素瓶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAirPotion</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础气流药剂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirPotion</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>气流药剂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TailwindPotion</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺风药剂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Draw,Damage_Windborne]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage_Windborne,Draw,Damage]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,1,2]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,1,3]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,1,3]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Draw,Damage_Self]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沟壑</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFissure</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Stun_Enemy,Damage,Draw]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,1,0]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,1,0]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,6,0]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沙暴</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSandstorm</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,5,5]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>基岩</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bedrock</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,8,1]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>热砂药剂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage,Buff_Burn_Enemy]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Buff_Burn_Enemy]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,6,3]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScorchingSandsPotion</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self_Focus,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,7,5]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1713,29 +1859,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2009,20 +2158,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.09765625" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="5" max="5" width="22.19921875" customWidth="1"/>
+    <col min="6" max="6" width="22.3984375" customWidth="1"/>
+    <col min="7" max="7" width="19.09765625" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="62.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.09765625" customWidth="1"/>
+    <col min="11" max="11" width="62.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2057,7 +2206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2092,7 +2241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2127,7 +2276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2147,7 +2296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -2182,7 +2331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2214,7 +2363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2246,7 +2395,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
         <v>318</v>
       </c>
@@ -2278,7 +2427,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
         <v>320</v>
       </c>
@@ -2311,7 +2460,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2319,19 +2468,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2366,7 +2515,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -2401,7 +2550,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>60</v>
       </c>
@@ -2430,13 +2579,13 @@
         <v>62</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>63</v>
+        <v>508</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -2471,7 +2620,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -2506,7 +2655,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
@@ -2541,7 +2690,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -2576,7 +2725,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
         <v>85</v>
       </c>
@@ -2611,7 +2760,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="2" t="s">
         <v>90</v>
       </c>
@@ -2646,7 +2795,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="2" t="s">
         <v>95</v>
       </c>
@@ -2681,7 +2830,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
@@ -2716,7 +2865,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="2" t="s">
         <v>106</v>
       </c>
@@ -2751,7 +2900,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
@@ -2786,7 +2935,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
@@ -2821,7 +2970,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="2" t="s">
         <v>118</v>
       </c>
@@ -2856,7 +3005,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -2891,7 +3040,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
         <v>127</v>
       </c>
@@ -2926,7 +3075,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
         <v>132</v>
       </c>
@@ -2961,7 +3110,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="3" t="s">
         <v>138</v>
       </c>
@@ -2996,7 +3145,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
         <v>143</v>
       </c>
@@ -3031,7 +3180,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="3" t="s">
         <v>147</v>
       </c>
@@ -3066,7 +3215,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="3" t="s">
         <v>151</v>
       </c>
@@ -3102,7 +3251,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3110,20 +3259,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3158,7 +3307,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>155</v>
       </c>
@@ -3193,7 +3342,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>159</v>
       </c>
@@ -3228,7 +3377,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
         <v>163</v>
       </c>
@@ -3263,7 +3412,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
         <v>169</v>
       </c>
@@ -3298,7 +3447,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>174</v>
       </c>
@@ -3333,7 +3482,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
         <v>178</v>
       </c>
@@ -3368,7 +3517,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
         <v>182</v>
       </c>
@@ -3403,7 +3552,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="2" t="s">
         <v>185</v>
       </c>
@@ -3438,7 +3587,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="2" t="s">
         <v>189</v>
       </c>
@@ -3473,7 +3622,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="2" t="s">
         <v>195</v>
       </c>
@@ -3508,7 +3657,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="2" t="s">
         <v>200</v>
       </c>
@@ -3543,7 +3692,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1">
       <c r="A14" s="2" t="s">
         <v>205</v>
       </c>
@@ -3578,7 +3727,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1">
       <c r="A15" s="2" t="s">
         <v>209</v>
       </c>
@@ -3613,7 +3762,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
@@ -3648,7 +3797,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="3" t="s">
         <v>218</v>
       </c>
@@ -3683,7 +3832,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
         <v>222</v>
       </c>
@@ -3718,7 +3867,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
         <v>227</v>
       </c>
@@ -3753,7 +3902,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="3" t="s">
         <v>232</v>
       </c>
@@ -3788,7 +3937,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
         <v>237</v>
       </c>
@@ -3823,7 +3972,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="3" t="s">
         <v>242</v>
       </c>
@@ -3858,7 +4007,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="3" t="s">
         <v>248</v>
       </c>
@@ -3893,17 +4042,17 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3911,20 +4060,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2441ED13-5DB1-49F6-B610-4785970FA9EB}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3959,7 +4108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="7" t="s">
         <v>362</v>
       </c>
@@ -3994,7 +4143,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="7" t="s">
         <v>363</v>
       </c>
@@ -4029,7 +4178,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="7" t="s">
         <v>364</v>
       </c>
@@ -4064,7 +4213,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="7" t="s">
         <v>365</v>
       </c>
@@ -4099,7 +4248,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="5" t="s">
         <v>366</v>
       </c>
@@ -4125,7 +4274,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>408</v>
+        <v>498</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>405</v>
@@ -4134,7 +4283,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="5" t="s">
         <v>367</v>
       </c>
@@ -4169,7 +4318,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="5" t="s">
         <v>368</v>
       </c>
@@ -4194,8 +4343,8 @@
       <c r="I9" s="2">
         <v>5</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>52</v>
+      <c r="J9" s="21" t="s">
+        <v>499</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>414</v>
@@ -4204,7 +4353,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="5" t="s">
         <v>369</v>
       </c>
@@ -4239,7 +4388,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="5" t="s">
         <v>370</v>
       </c>
@@ -4274,7 +4423,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="5" t="s">
         <v>371</v>
       </c>
@@ -4300,7 +4449,7 @@
         <v>5</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>431</v>
@@ -4309,7 +4458,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="5" t="s">
         <v>372</v>
       </c>
@@ -4344,7 +4493,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>373</v>
       </c>
@@ -4379,7 +4528,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>374</v>
       </c>
@@ -4414,7 +4563,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="5" t="s">
         <v>375</v>
       </c>
@@ -4449,7 +4598,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="6" t="s">
         <v>376</v>
       </c>
@@ -4484,7 +4633,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="6" t="s">
         <v>377</v>
       </c>
@@ -4519,7 +4668,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="6" t="s">
         <v>378</v>
       </c>
@@ -4554,12 +4703,12 @@
         <v>454</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="6" t="s">
         <v>379</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>233</v>
+        <v>496</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -4567,34 +4716,34 @@
       <c r="E21" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>33</v>
+      <c r="F21" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>401</v>
+      <c r="H21" s="20" t="s">
+        <v>425</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>234</v>
+        <v>500</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>235</v>
+        <v>497</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="6" t="s">
         <v>380</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>238</v>
+        <v>502</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -4602,34 +4751,34 @@
       <c r="E22" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>33</v>
+      <c r="F22" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>401</v>
+      <c r="H22" s="20" t="s">
+        <v>425</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>239</v>
+        <v>503</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>240</v>
+        <v>413</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="6" t="s">
         <v>381</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -4637,34 +4786,34 @@
       <c r="E23" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>33</v>
+      <c r="F23" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>401</v>
+      <c r="H23" s="20" t="s">
+        <v>402</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>245</v>
+        <v>510</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>246</v>
+        <v>509</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="6" t="s">
         <v>382</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>249</v>
+        <v>505</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -4672,8 +4821,8 @@
       <c r="E24" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>33</v>
+      <c r="F24" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
@@ -4685,26 +4834,26 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>250</v>
+        <v>513</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>251</v>
+        <v>512</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4712,20 +4861,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C02A9BF-5C11-492C-BF77-FB0B6AF52D8A}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4760,12 +4909,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="7" t="s">
         <v>457</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>355</v>
+        <v>481</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>356</v>
@@ -4792,15 +4941,15 @@
         <v>413</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="7" t="s">
         <v>458</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>383</v>
+        <v>483</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>356</v>
@@ -4814,28 +4963,28 @@
       <c r="G3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="18" t="s">
-        <v>402</v>
+      <c r="H3" s="19" t="s">
+        <v>480</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>427</v>
+        <v>491</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>385</v>
+        <v>490</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="7" t="s">
         <v>459</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>356</v>
@@ -4849,28 +4998,28 @@
       <c r="G4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>402</v>
+      <c r="H4" s="19" t="s">
+        <v>480</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>386</v>
+        <v>492</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>385</v>
+        <v>489</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="7" t="s">
         <v>460</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>388</v>
+        <v>487</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>356</v>
@@ -4884,23 +5033,23 @@
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="18" t="s">
-        <v>402</v>
+      <c r="H5" s="19" t="s">
+        <v>446</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>391</v>
+        <v>494</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="5" t="s">
         <v>461</v>
       </c>
@@ -4935,7 +5084,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="5" t="s">
         <v>462</v>
       </c>
@@ -4970,7 +5119,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="5" t="s">
         <v>463</v>
       </c>
@@ -5005,7 +5154,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="5" t="s">
         <v>464</v>
       </c>
@@ -5040,7 +5189,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="5" t="s">
         <v>465</v>
       </c>
@@ -5075,7 +5224,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="5" t="s">
         <v>466</v>
       </c>
@@ -5110,7 +5259,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="5" t="s">
         <v>467</v>
       </c>
@@ -5145,7 +5294,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>468</v>
       </c>
@@ -5180,7 +5329,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>469</v>
       </c>
@@ -5215,7 +5364,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="5" t="s">
         <v>470</v>
       </c>
@@ -5250,7 +5399,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="6" t="s">
         <v>471</v>
       </c>
@@ -5285,7 +5434,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="6" t="s">
         <v>472</v>
       </c>
@@ -5320,7 +5469,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="6" t="s">
         <v>473</v>
       </c>
@@ -5355,7 +5504,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="6" t="s">
         <v>474</v>
       </c>
@@ -5390,7 +5539,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="6" t="s">
         <v>475</v>
       </c>
@@ -5425,7 +5574,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="6" t="s">
         <v>476</v>
       </c>
@@ -5460,7 +5609,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="6" t="s">
         <v>477</v>
       </c>
@@ -5495,17 +5644,17 @@
         <v>390</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5513,19 +5662,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="4" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="45.77734375" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" customWidth="1"/>
+    <col min="10" max="10" width="12.296875" customWidth="1"/>
+    <col min="11" max="11" width="45.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5560,7 +5709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>253</v>
       </c>
@@ -5595,7 +5744,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>260</v>
       </c>
@@ -5630,7 +5779,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="2" customFormat="1">
       <c r="A5" s="2" t="s">
         <v>266</v>
       </c>
@@ -5665,7 +5814,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
         <v>271</v>
       </c>
@@ -5700,7 +5849,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>276</v>
       </c>
@@ -5735,7 +5884,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
         <v>280</v>
       </c>
@@ -5770,7 +5919,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
         <v>285</v>
       </c>
@@ -5805,7 +5954,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="3" customFormat="1">
       <c r="A11" s="3" t="s">
         <v>290</v>
       </c>
@@ -5840,7 +5989,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="3" customFormat="1">
       <c r="A12" s="3" t="s">
         <v>295</v>
       </c>
@@ -5875,7 +6024,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="3" customFormat="1">
       <c r="A13" s="3" t="s">
         <v>300</v>
       </c>
@@ -5910,7 +6059,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="3" customFormat="1">
       <c r="A14" s="3" t="s">
         <v>306</v>
       </c>
@@ -5945,7 +6094,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="3" customFormat="1">
       <c r="A15" s="3" t="s">
         <v>311</v>
       </c>
@@ -5981,7 +6130,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328DAE95-1F2E-4978-8011-C005C1BE38FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E35D1-16C6-4B71-8D4C-E356ACD19DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="518">
   <si>
     <t>Id</t>
   </si>
@@ -428,1327 +428,1352 @@
     <t>[0,2,5]</t>
   </si>
   <si>
+    <t>脉冲药剂</t>
+  </si>
+  <si>
+    <t>F203</t>
+  </si>
+  <si>
+    <t>Supernova</t>
+  </si>
+  <si>
+    <t>[4,0,0,0]</t>
+  </si>
+  <si>
+    <t>[5,13,1]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Enemy,Damage,Draw]</t>
+  </si>
+  <si>
+    <t>超新星</t>
+  </si>
+  <si>
+    <t>F204</t>
+  </si>
+  <si>
+    <t>MidasPotion</t>
+  </si>
+  <si>
+    <t>[3,2,9]</t>
+  </si>
+  <si>
+    <t>[Draw_Unstable,Buff_Burn_Self,Damage_Unstable]</t>
+  </si>
+  <si>
+    <t>点金药剂</t>
+  </si>
+  <si>
+    <t>F205</t>
+  </si>
+  <si>
+    <t>[6,6,6]</t>
+  </si>
+  <si>
+    <t>[Damage,Damage_Self,Damage_Unstable]</t>
+  </si>
+  <si>
+    <t>瓶装火球</t>
+  </si>
+  <si>
+    <t>F206</t>
+  </si>
+  <si>
+    <t>[5,6,5]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Ignite]</t>
+  </si>
+  <si>
+    <t>瓶装凤凰</t>
+  </si>
+  <si>
+    <t>F207</t>
+  </si>
+  <si>
+    <t>[Draw,Buff_Burn_Self,Damage_Self]</t>
+  </si>
+  <si>
+    <t>瓶装猿猴精怪</t>
+  </si>
+  <si>
+    <t>W100</t>
+  </si>
+  <si>
+    <t>WaterElementBottle</t>
+  </si>
+  <si>
+    <t>[0,1,0,0]</t>
+  </si>
+  <si>
+    <t>水元素瓶</t>
+  </si>
+  <si>
+    <t>W101</t>
+  </si>
+  <si>
+    <t>[4,1,3]</t>
+  </si>
+  <si>
+    <t>[Damage,Damage,Damage_Madness]</t>
+  </si>
+  <si>
+    <t>基础水流药剂</t>
+  </si>
+  <si>
+    <t>W102</t>
+  </si>
+  <si>
+    <t>WaterPotion</t>
+  </si>
+  <si>
+    <t>[false,true,false,false]</t>
+  </si>
+  <si>
+    <t>[7,1,4]</t>
+  </si>
+  <si>
+    <t>[Damage,Discard,Damage_Madness]</t>
+  </si>
+  <si>
+    <t>水流药剂</t>
+  </si>
+  <si>
+    <t>W103</t>
+  </si>
+  <si>
+    <t>SpeedPotion</t>
+  </si>
+  <si>
+    <t>[2,1,1]</t>
+  </si>
+  <si>
+    <t>[Buff_Quickness_Self,Discard,Draw]</t>
+  </si>
+  <si>
+    <t>速度药剂</t>
+  </si>
+  <si>
+    <t>W104</t>
+  </si>
+  <si>
+    <t>[5,1,0]</t>
+  </si>
+  <si>
+    <t>[Heal,Heal,Draw]</t>
+  </si>
+  <si>
+    <t>治疗药剂</t>
+  </si>
+  <si>
+    <t>W105</t>
+  </si>
+  <si>
+    <t>[6,1,1]</t>
+  </si>
+  <si>
+    <t>[Damage,Neutralize,Discard]</t>
+  </si>
+  <si>
+    <t>中和药剂</t>
+  </si>
+  <si>
+    <t>W106</t>
+  </si>
+  <si>
+    <t>[Discard,Draw,Recycle]</t>
+  </si>
+  <si>
+    <t>循环药剂</t>
+  </si>
+  <si>
+    <t>W107</t>
+  </si>
+  <si>
+    <t>[1,5,2]</t>
+  </si>
+  <si>
+    <t>[Discard,Damage_Peace,Draw]</t>
+  </si>
+  <si>
+    <t>冥思药剂</t>
+  </si>
+  <si>
+    <t>W108</t>
+  </si>
+  <si>
+    <t>EbbPotion</t>
+  </si>
+  <si>
+    <t>[0,2,0,0]</t>
+  </si>
+  <si>
+    <t>[8,4,3]</t>
+  </si>
+  <si>
+    <t>[Damage_Madness,Damage,Draw_Madness]</t>
+  </si>
+  <si>
+    <t>潮涨</t>
+  </si>
+  <si>
+    <t>W109</t>
+  </si>
+  <si>
+    <t>FlowPotion</t>
+  </si>
+  <si>
+    <t>[0,1,5]</t>
+  </si>
+  <si>
+    <t>[Discard,Discard,Damage_Peace]</t>
+  </si>
+  <si>
+    <t>潮落</t>
+  </si>
+  <si>
+    <t>W110</t>
+  </si>
+  <si>
+    <t>SacredSpringWater</t>
+  </si>
+  <si>
+    <t>[4,3,2]</t>
+  </si>
+  <si>
+    <t>[Buff_Quickness_Self,Neutralize,Neutralize]</t>
+  </si>
+  <si>
+    <t>圣洁的泉水</t>
+  </si>
+  <si>
+    <t>W111</t>
+  </si>
+  <si>
+    <t>[6,3,6]</t>
+  </si>
+  <si>
+    <t>[Damage_Madness,Damage,Damage_Peace]</t>
+  </si>
+  <si>
+    <t>智者的悲叹</t>
+  </si>
+  <si>
+    <t>W112</t>
+  </si>
+  <si>
+    <t>OceanElementBottle</t>
+  </si>
+  <si>
+    <t>[Heal,Draw,Discard]</t>
+  </si>
+  <si>
+    <t>海洋元素瓶</t>
+  </si>
+  <si>
+    <t>W113</t>
+  </si>
+  <si>
+    <t>EndlessWave</t>
+  </si>
+  <si>
+    <t>[8,1,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Madness,Discard_Madness,Draw]</t>
+  </si>
+  <si>
+    <t>不休的浪潮</t>
+  </si>
+  <si>
+    <t>W201</t>
+  </si>
+  <si>
+    <t>GreaterWaterPotion</t>
+  </si>
+  <si>
+    <t>[9,1,7]</t>
+  </si>
+  <si>
+    <t>高等水流药剂</t>
+  </si>
+  <si>
+    <t>W202</t>
+  </si>
+  <si>
+    <t>LionsTears</t>
+  </si>
+  <si>
+    <t>[1,0,0]</t>
+  </si>
+  <si>
+    <t>[LED_Water,Damage,Heal]</t>
+  </si>
+  <si>
+    <t>狮子的眼泪</t>
+  </si>
+  <si>
+    <t>W203</t>
+  </si>
+  <si>
+    <t>ForbiddenDroplet</t>
+  </si>
+  <si>
+    <t>[1,4,1]</t>
+  </si>
+  <si>
+    <t>[Discard,Neutralize,Draw_Peace]</t>
+  </si>
+  <si>
+    <t>禁忌的一滴</t>
+  </si>
+  <si>
+    <t>W204</t>
+  </si>
+  <si>
+    <t>BottledSwirl</t>
+  </si>
+  <si>
+    <t>[6,2,1]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Stun_Enemy,Buff_Stun_Enemy_Madness]</t>
+  </si>
+  <si>
+    <t>瓶装漩涡</t>
+  </si>
+  <si>
+    <t>W205</t>
+  </si>
+  <si>
+    <t>BottledOasis</t>
+  </si>
+  <si>
+    <t>[5,1,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Peace,Draw_Peace,Quickness_Peace]</t>
+  </si>
+  <si>
+    <t>瓶装绿洲</t>
+  </si>
+  <si>
+    <t>W206</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
+  </si>
+  <si>
+    <t>[0,3,0,0]</t>
+  </si>
+  <si>
+    <t>[8,3,6]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Stun_Enemy,Discard]</t>
+  </si>
+  <si>
+    <t>海啸</t>
+  </si>
+  <si>
+    <t>W207</t>
+  </si>
+  <si>
+    <t>ConstantFlux</t>
+  </si>
+  <si>
+    <t>[5,5,5]</t>
+  </si>
+  <si>
+    <t>[Heal_Madness,Discard_Madness,Draw_Madness]</t>
+  </si>
+  <si>
+    <t>流转的呼吸</t>
+  </si>
+  <si>
+    <t>FW100</t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>Fire_Water</t>
+  </si>
+  <si>
+    <t>[1,1,0,0]</t>
+  </si>
+  <si>
+    <t>[1,1,0]</t>
+  </si>
+  <si>
+    <t>[Damage,Buff_Burn_Self,Heal]</t>
+  </si>
+  <si>
+    <t>乙醇</t>
+  </si>
+  <si>
+    <t>FW101</t>
+  </si>
+  <si>
+    <t>Lorazepam</t>
+  </si>
+  <si>
+    <t>[true,true,false,false]</t>
+  </si>
+  <si>
+    <t>[3,2,4]</t>
+  </si>
+  <si>
+    <t>[Buff_Calm_Self,Draw,Heal]</t>
+  </si>
+  <si>
+    <t>劳拉西泮</t>
+  </si>
+  <si>
+    <t>FW102</t>
+  </si>
+  <si>
+    <t>DryIce</t>
+  </si>
+  <si>
+    <t>[5,4,2]</t>
+  </si>
+  <si>
+    <t>[Damage_Cooldown,Damage,Buff_Quickness_Self]</t>
+  </si>
+  <si>
+    <t>干冰</t>
+  </si>
+  <si>
+    <t>FW103</t>
+  </si>
+  <si>
+    <t>ConcentratedNitricAcid</t>
+  </si>
+  <si>
+    <t>[5,3,4]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Damage]</t>
+  </si>
+  <si>
+    <t>浓硝酸</t>
+  </si>
+  <si>
+    <t>FW104</t>
+  </si>
+  <si>
+    <t>Ammonia</t>
+  </si>
+  <si>
+    <t>[Damage_Cooldown,Draw,Damage]</t>
+  </si>
+  <si>
+    <t>液态氨</t>
+  </si>
+  <si>
+    <t>FW105</t>
+  </si>
+  <si>
+    <t>Dopamine</t>
+  </si>
+  <si>
+    <t>[4,1,4]</t>
+  </si>
+  <si>
+    <t>[Quickness_Peace,Buff_Burn_Self,Heal_Madness]</t>
+  </si>
+  <si>
+    <t>多巴胺</t>
+  </si>
+  <si>
+    <t>FW106</t>
+  </si>
+  <si>
+    <t>Methane</t>
+  </si>
+  <si>
+    <t>[3,9,3]</t>
+  </si>
+  <si>
+    <t>[Draw_Unstable,Damage_Cooldown,Buff_Burn_Self]</t>
+  </si>
+  <si>
+    <t>甲烷</t>
+  </si>
+  <si>
+    <t>FW201</t>
+  </si>
+  <si>
+    <t>SodiumBicarbonate</t>
+  </si>
+  <si>
+    <t>[3,3,5]</t>
+  </si>
+  <si>
+    <t>[Draw_Cooldown,Neutralize,Heal]</t>
+  </si>
+  <si>
+    <t>碳酸氢钠</t>
+  </si>
+  <si>
+    <t>FW202</t>
+  </si>
+  <si>
+    <t>Trinitrotoluene</t>
+  </si>
+  <si>
+    <t>[4,10,1]</t>
+  </si>
+  <si>
+    <t>[Buff_Burn_Self,Damage,Elemental_Water]</t>
+  </si>
+  <si>
+    <t>三硝基甲苯</t>
+  </si>
+  <si>
+    <t>FW203</t>
+  </si>
+  <si>
+    <t>Graphene</t>
+  </si>
+  <si>
+    <t>[2,1,0,0]</t>
+  </si>
+  <si>
+    <t>[8,1,4]</t>
+  </si>
+  <si>
+    <t>[Ignite_Cooldown,Elemental_Water_Madness,Damage]</t>
+  </si>
+  <si>
+    <t>石墨烯</t>
+  </si>
+  <si>
+    <t>FW204</t>
+  </si>
+  <si>
+    <t>TaqDNAPolymerase</t>
+  </si>
+  <si>
+    <t>[2,2,5]</t>
+  </si>
+  <si>
+    <t>[Draw_Cooldown,Catalyze,Catalyze]</t>
+  </si>
+  <si>
+    <t>Taq酶</t>
+  </si>
+  <si>
+    <t>FW205</t>
+  </si>
+  <si>
+    <t>Chloroform</t>
+  </si>
+  <si>
+    <t>[1,1,5]</t>
+  </si>
+  <si>
+    <t>[Elemental_Water,Elemental_Fire,Damage_Self]</t>
+  </si>
+  <si>
+    <t>氯仿</t>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>B01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch_Test1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>Branch_Test2</t>
+  </si>
+  <si>
+    <t>InternalBurningPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnstableFirePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmberPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExternalBurningPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFireball</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledPhoenix</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSimianSpirit</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FireElementBottle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BasicFirePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FirePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.PowerPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.HeatTherapy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.CatalyzePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.ScalePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.FlashPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.WillOWisp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BlastPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.InternalBurningPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.UnstableFirePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.EmberPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.ExternalBurningPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.GreaterFirePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.PulsePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.SuperNova</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.MidasPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledFireball</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledPhoenix</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Fire/Card.BottledSimianSpirit</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.WaterElementBottle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicWaterPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.BasicWaterPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.WaterPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.SpeedPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthElementBottle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Test</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false,true,false]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>土元素瓶</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础大地药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>E100</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>E101</t>
+  </si>
+  <si>
+    <t>E102</t>
+  </si>
+  <si>
+    <t>E103</t>
+  </si>
+  <si>
+    <t>E104</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>E105</t>
+  </si>
+  <si>
+    <t>E106</t>
+  </si>
+  <si>
+    <t>E107</t>
+  </si>
+  <si>
+    <t>E108</t>
+  </si>
+  <si>
+    <t>E109</t>
+  </si>
+  <si>
+    <t>E110</t>
+  </si>
+  <si>
+    <t>E111</t>
+  </si>
+  <si>
+    <t>E112</t>
+  </si>
+  <si>
+    <t>E113</t>
+  </si>
+  <si>
+    <t>E201</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>E202</t>
+  </si>
+  <si>
+    <t>E203</t>
+  </si>
+  <si>
+    <t>E204</t>
+  </si>
+  <si>
+    <t>E205</t>
+  </si>
+  <si>
+    <t>E206</t>
+  </si>
+  <si>
+    <t>E207</t>
+  </si>
+  <si>
+    <t>BasicEarthPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,3,2]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地核药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthCorePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,3,3]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定占位</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.HealPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeutralizePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.NeutralizePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CyclePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalmMindPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.CalmMindPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LamentOfTheWise</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card/Water/Card.LamentOfTheWise</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,1,0]</t>
+  </si>
+  <si>
+    <t>[0,0,1,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterEarthPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>VitalityPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Heal,Draw]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>健体药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等大地药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,1,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁骨药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IronbonePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7,5,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage,Damage]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Stun_Enemy,Damage]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>束缚药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShacklePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>反射药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReflectionPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Draw,Buff_Reflect_Self,Damage]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,6,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StoneskinPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>石肤药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[12,2,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,2,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,3,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,3,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[14,10,9]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FocusPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Draw_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,8,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Reflect_Self,Draw,Damage]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpikePotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,1,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地壳药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrustPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,3,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地能药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPowerPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Draw,Discard]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[9,2,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>息壤</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,0,3]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfEarth</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野之息</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfTheWild</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoarOfTheEarth</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>土石咆哮</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Damage_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,5,6]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>A100</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>A104</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>A106</t>
+  </si>
+  <si>
+    <t>A107</t>
+  </si>
+  <si>
+    <t>A108</t>
+  </si>
+  <si>
+    <t>A109</t>
+  </si>
+  <si>
+    <t>A110</t>
+  </si>
+  <si>
+    <t>A111</t>
+  </si>
+  <si>
+    <t>A112</t>
+  </si>
+  <si>
+    <t>A113</t>
+  </si>
+  <si>
+    <t>A201</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>A203</t>
+  </si>
+  <si>
+    <t>A204</t>
+  </si>
+  <si>
+    <t>A205</t>
+  </si>
+  <si>
+    <t>A206</t>
+  </si>
+  <si>
+    <t>A207</t>
+  </si>
+  <si>
+    <t>Air</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false,false,true]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirElementBottle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>气元素瓶</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAirPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础气流药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>气流药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TailwindPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺风药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Draw,Damage_Windborne]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage_Windborne,Draw,Damage]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,1,2]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,1,3]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,1,3]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Draw,Damage_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沟壑</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFissure</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Stun_Enemy,Damage,Draw]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,1,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,6,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沙暴</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSandstorm</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,5,5]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>基岩</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bedrock</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,8,1]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>热砂药剂</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage,Buff_Burn_Enemy]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Damage_Focus,Buff_Burn_Enemy]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,6,3]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScorchingSandsPotion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self_Focus,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,7,5]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,2,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7,1,0]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Buff_Sturdy_Self,Damage,Buff_Reflect_Self]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[16,7,6]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>[Draw,Elemental_Fire,Buff_Burn_Self]</t>
-  </si>
-  <si>
-    <t>脉冲药剂</t>
-  </si>
-  <si>
-    <t>F203</t>
-  </si>
-  <si>
-    <t>Supernova</t>
-  </si>
-  <si>
-    <t>[4,0,0,0]</t>
-  </si>
-  <si>
-    <t>[5,13,1]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Enemy,Damage,Draw]</t>
-  </si>
-  <si>
-    <t>超新星</t>
-  </si>
-  <si>
-    <t>F204</t>
-  </si>
-  <si>
-    <t>MidasPotion</t>
-  </si>
-  <si>
-    <t>[3,2,9]</t>
-  </si>
-  <si>
-    <t>[Draw_Unstable,Buff_Burn_Self,Damage_Unstable]</t>
-  </si>
-  <si>
-    <t>点金药剂</t>
-  </si>
-  <si>
-    <t>F205</t>
-  </si>
-  <si>
-    <t>[6,6,6]</t>
-  </si>
-  <si>
-    <t>[Damage,Damage_Self,Damage_Unstable]</t>
-  </si>
-  <si>
-    <t>瓶装火球</t>
-  </si>
-  <si>
-    <t>F206</t>
-  </si>
-  <si>
-    <t>[5,6,5]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Ignite]</t>
-  </si>
-  <si>
-    <t>瓶装凤凰</t>
-  </si>
-  <si>
-    <t>F207</t>
-  </si>
-  <si>
-    <t>[3,5,0]</t>
-  </si>
-  <si>
-    <t>[Draw,Buff_Burn_Self,Damage_Self]</t>
-  </si>
-  <si>
-    <t>瓶装猿猴精怪</t>
-  </si>
-  <si>
-    <t>W100</t>
-  </si>
-  <si>
-    <t>WaterElementBottle</t>
-  </si>
-  <si>
-    <t>[0,1,0,0]</t>
-  </si>
-  <si>
-    <t>水元素瓶</t>
-  </si>
-  <si>
-    <t>W101</t>
-  </si>
-  <si>
-    <t>[4,1,3]</t>
-  </si>
-  <si>
-    <t>[Damage,Damage,Damage_Madness]</t>
-  </si>
-  <si>
-    <t>基础水流药剂</t>
-  </si>
-  <si>
-    <t>W102</t>
-  </si>
-  <si>
-    <t>WaterPotion</t>
-  </si>
-  <si>
-    <t>[false,true,false,false]</t>
-  </si>
-  <si>
-    <t>[7,1,4]</t>
-  </si>
-  <si>
-    <t>[Damage,Discard,Damage_Madness]</t>
-  </si>
-  <si>
-    <t>水流药剂</t>
-  </si>
-  <si>
-    <t>W103</t>
-  </si>
-  <si>
-    <t>SpeedPotion</t>
-  </si>
-  <si>
-    <t>[2,1,1]</t>
-  </si>
-  <si>
-    <t>[Buff_Quickness_Self,Discard,Draw]</t>
-  </si>
-  <si>
-    <t>速度药剂</t>
-  </si>
-  <si>
-    <t>W104</t>
-  </si>
-  <si>
-    <t>[5,1,0]</t>
-  </si>
-  <si>
-    <t>[Heal,Heal,Draw]</t>
-  </si>
-  <si>
-    <t>治疗药剂</t>
-  </si>
-  <si>
-    <t>W105</t>
-  </si>
-  <si>
-    <t>[6,1,1]</t>
-  </si>
-  <si>
-    <t>[Damage,Neutralize,Discard]</t>
-  </si>
-  <si>
-    <t>中和药剂</t>
-  </si>
-  <si>
-    <t>W106</t>
-  </si>
-  <si>
-    <t>[Discard,Draw,Recycle]</t>
-  </si>
-  <si>
-    <t>循环药剂</t>
-  </si>
-  <si>
-    <t>W107</t>
-  </si>
-  <si>
-    <t>[1,5,2]</t>
-  </si>
-  <si>
-    <t>[Discard,Damage_Peace,Draw]</t>
-  </si>
-  <si>
-    <t>冥思药剂</t>
-  </si>
-  <si>
-    <t>W108</t>
-  </si>
-  <si>
-    <t>EbbPotion</t>
-  </si>
-  <si>
-    <t>[0,2,0,0]</t>
-  </si>
-  <si>
-    <t>[8,4,3]</t>
-  </si>
-  <si>
-    <t>[Damage_Madness,Damage,Draw_Madness]</t>
-  </si>
-  <si>
-    <t>潮涨</t>
-  </si>
-  <si>
-    <t>W109</t>
-  </si>
-  <si>
-    <t>FlowPotion</t>
-  </si>
-  <si>
-    <t>[0,1,5]</t>
-  </si>
-  <si>
-    <t>[Discard,Discard,Damage_Peace]</t>
-  </si>
-  <si>
-    <t>潮落</t>
-  </si>
-  <si>
-    <t>W110</t>
-  </si>
-  <si>
-    <t>SacredSpringWater</t>
-  </si>
-  <si>
-    <t>[4,3,2]</t>
-  </si>
-  <si>
-    <t>[Buff_Quickness_Self,Neutralize,Neutralize]</t>
-  </si>
-  <si>
-    <t>圣洁的泉水</t>
-  </si>
-  <si>
-    <t>W111</t>
-  </si>
-  <si>
-    <t>[6,3,6]</t>
-  </si>
-  <si>
-    <t>[Damage_Madness,Damage,Damage_Peace]</t>
-  </si>
-  <si>
-    <t>智者的悲叹</t>
-  </si>
-  <si>
-    <t>W112</t>
-  </si>
-  <si>
-    <t>OceanElementBottle</t>
-  </si>
-  <si>
-    <t>[Heal,Draw,Discard]</t>
-  </si>
-  <si>
-    <t>海洋元素瓶</t>
-  </si>
-  <si>
-    <t>W113</t>
-  </si>
-  <si>
-    <t>EndlessWave</t>
-  </si>
-  <si>
-    <t>[8,1,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Madness,Discard_Madness,Draw]</t>
-  </si>
-  <si>
-    <t>不休的浪潮</t>
-  </si>
-  <si>
-    <t>W201</t>
-  </si>
-  <si>
-    <t>GreaterWaterPotion</t>
-  </si>
-  <si>
-    <t>[9,1,7]</t>
-  </si>
-  <si>
-    <t>高等水流药剂</t>
-  </si>
-  <si>
-    <t>W202</t>
-  </si>
-  <si>
-    <t>LionsTears</t>
-  </si>
-  <si>
-    <t>[1,0,0]</t>
-  </si>
-  <si>
-    <t>[LED_Water,Damage,Heal]</t>
-  </si>
-  <si>
-    <t>狮子的眼泪</t>
-  </si>
-  <si>
-    <t>W203</t>
-  </si>
-  <si>
-    <t>ForbiddenDroplet</t>
-  </si>
-  <si>
-    <t>[1,4,1]</t>
-  </si>
-  <si>
-    <t>[Discard,Neutralize,Draw_Peace]</t>
-  </si>
-  <si>
-    <t>禁忌的一滴</t>
-  </si>
-  <si>
-    <t>W204</t>
-  </si>
-  <si>
-    <t>BottledSwirl</t>
-  </si>
-  <si>
-    <t>[6,2,1]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Stun_Enemy,Buff_Stun_Enemy_Madness]</t>
-  </si>
-  <si>
-    <t>瓶装漩涡</t>
-  </si>
-  <si>
-    <t>W205</t>
-  </si>
-  <si>
-    <t>BottledOasis</t>
-  </si>
-  <si>
-    <t>[5,1,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Peace,Draw_Peace,Quickness_Peace]</t>
-  </si>
-  <si>
-    <t>瓶装绿洲</t>
-  </si>
-  <si>
-    <t>W206</t>
-  </si>
-  <si>
-    <t>Tsunami</t>
-  </si>
-  <si>
-    <t>[0,3,0,0]</t>
-  </si>
-  <si>
-    <t>[8,3,6]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Stun_Enemy,Discard]</t>
-  </si>
-  <si>
-    <t>海啸</t>
-  </si>
-  <si>
-    <t>W207</t>
-  </si>
-  <si>
-    <t>ConstantFlux</t>
-  </si>
-  <si>
-    <t>[5,5,5]</t>
-  </si>
-  <si>
-    <t>[Heal_Madness,Discard_Madness,Draw_Madness]</t>
-  </si>
-  <si>
-    <t>流转的呼吸</t>
-  </si>
-  <si>
-    <t>FW100</t>
-  </si>
-  <si>
-    <t>Ethanol</t>
-  </si>
-  <si>
-    <t>Fire_Water</t>
-  </si>
-  <si>
-    <t>[1,1,0,0]</t>
-  </si>
-  <si>
-    <t>[1,1,0]</t>
-  </si>
-  <si>
-    <t>[Damage,Buff_Burn_Self,Heal]</t>
-  </si>
-  <si>
-    <t>乙醇</t>
-  </si>
-  <si>
-    <t>FW101</t>
-  </si>
-  <si>
-    <t>Lorazepam</t>
-  </si>
-  <si>
-    <t>[true,true,false,false]</t>
-  </si>
-  <si>
-    <t>[3,2,4]</t>
-  </si>
-  <si>
-    <t>[Buff_Calm_Self,Draw,Heal]</t>
-  </si>
-  <si>
-    <t>劳拉西泮</t>
-  </si>
-  <si>
-    <t>FW102</t>
-  </si>
-  <si>
-    <t>DryIce</t>
-  </si>
-  <si>
-    <t>[5,4,2]</t>
-  </si>
-  <si>
-    <t>[Damage_Cooldown,Damage,Buff_Quickness_Self]</t>
-  </si>
-  <si>
-    <t>干冰</t>
-  </si>
-  <si>
-    <t>FW103</t>
-  </si>
-  <si>
-    <t>ConcentratedNitricAcid</t>
-  </si>
-  <si>
-    <t>[5,3,4]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Enemy,Buff_Burn_Self,Damage]</t>
-  </si>
-  <si>
-    <t>浓硝酸</t>
-  </si>
-  <si>
-    <t>FW104</t>
-  </si>
-  <si>
-    <t>Ammonia</t>
-  </si>
-  <si>
-    <t>[Damage_Cooldown,Draw,Damage]</t>
-  </si>
-  <si>
-    <t>液态氨</t>
-  </si>
-  <si>
-    <t>FW105</t>
-  </si>
-  <si>
-    <t>Dopamine</t>
-  </si>
-  <si>
-    <t>[4,1,4]</t>
-  </si>
-  <si>
-    <t>[Quickness_Peace,Buff_Burn_Self,Heal_Madness]</t>
-  </si>
-  <si>
-    <t>多巴胺</t>
-  </si>
-  <si>
-    <t>FW106</t>
-  </si>
-  <si>
-    <t>Methane</t>
-  </si>
-  <si>
-    <t>[3,9,3]</t>
-  </si>
-  <si>
-    <t>[Draw_Unstable,Damage_Cooldown,Buff_Burn_Self]</t>
-  </si>
-  <si>
-    <t>甲烷</t>
-  </si>
-  <si>
-    <t>FW201</t>
-  </si>
-  <si>
-    <t>SodiumBicarbonate</t>
-  </si>
-  <si>
-    <t>[3,3,5]</t>
-  </si>
-  <si>
-    <t>[Draw_Cooldown,Neutralize,Heal]</t>
-  </si>
-  <si>
-    <t>碳酸氢钠</t>
-  </si>
-  <si>
-    <t>FW202</t>
-  </si>
-  <si>
-    <t>Trinitrotoluene</t>
-  </si>
-  <si>
-    <t>[4,10,1]</t>
-  </si>
-  <si>
-    <t>[Buff_Burn_Self,Damage,Elemental_Water]</t>
-  </si>
-  <si>
-    <t>三硝基甲苯</t>
-  </si>
-  <si>
-    <t>FW203</t>
-  </si>
-  <si>
-    <t>Graphene</t>
-  </si>
-  <si>
-    <t>[2,1,0,0]</t>
-  </si>
-  <si>
-    <t>[8,1,4]</t>
-  </si>
-  <si>
-    <t>[Ignite_Cooldown,Elemental_Water_Madness,Damage]</t>
-  </si>
-  <si>
-    <t>石墨烯</t>
-  </si>
-  <si>
-    <t>FW204</t>
-  </si>
-  <si>
-    <t>TaqDNAPolymerase</t>
-  </si>
-  <si>
-    <t>[2,2,5]</t>
-  </si>
-  <si>
-    <t>[Draw_Cooldown,Catalyze,Catalyze]</t>
-  </si>
-  <si>
-    <t>Taq酶</t>
-  </si>
-  <si>
-    <t>FW205</t>
-  </si>
-  <si>
-    <t>Chloroform</t>
-  </si>
-  <si>
-    <t>[1,1,5]</t>
-  </si>
-  <si>
-    <t>[Elemental_Water,Elemental_Fire,Damage_Self]</t>
-  </si>
-  <si>
-    <t>氯仿</t>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>B01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch_Test1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>B02</t>
-  </si>
-  <si>
-    <t>Branch_Test2</t>
-  </si>
-  <si>
-    <t>InternalBurningPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnstableFirePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmberPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledFireball</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledPhoenix</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicWaterPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthElementBottle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Test</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[false,false,true,false]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>土元素瓶</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础大地药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>E100</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>E101</t>
-  </si>
-  <si>
-    <t>E102</t>
-  </si>
-  <si>
-    <t>E103</t>
-  </si>
-  <si>
-    <t>E104</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>E105</t>
-  </si>
-  <si>
-    <t>E106</t>
-  </si>
-  <si>
-    <t>E107</t>
-  </si>
-  <si>
-    <t>E108</t>
-  </si>
-  <si>
-    <t>E109</t>
-  </si>
-  <si>
-    <t>E110</t>
-  </si>
-  <si>
-    <t>E111</t>
-  </si>
-  <si>
-    <t>E112</t>
-  </si>
-  <si>
-    <t>E113</t>
-  </si>
-  <si>
-    <t>E201</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>E202</t>
-  </si>
-  <si>
-    <t>E203</t>
-  </si>
-  <si>
-    <t>E204</t>
-  </si>
-  <si>
-    <t>E205</t>
-  </si>
-  <si>
-    <t>E206</t>
-  </si>
-  <si>
-    <t>E207</t>
-  </si>
-  <si>
-    <t>BasicEarthPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,3,2]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>地核药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthCorePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,3,3]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>待定占位</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeutralizePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CyclePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalmMindPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>LamentOfTheWise</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,0,1,0]</t>
-  </si>
-  <si>
-    <t>[0,0,1,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>VitalityPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>健体药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等大地药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,1,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁骨药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IronbonePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[7,5,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>束缚药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShacklePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>反射药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReflectionPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1,6,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneskinPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>石肤药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[12,2,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,0,2,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,0,3,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,3,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[14,10,9]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>集中药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>FocusPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage_Focus,Draw_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,8,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Reflect_Self,Draw,Damage]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>地刺药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpikePotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,1,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>地壳药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CrustPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,3,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>地能药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthPowerPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self,Draw,Discard]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[9,2,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>息壤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,0,0,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,0,3]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreathOfEarth</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒野之息</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreathOfTheWild</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>土石咆哮</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,5,6]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>A100</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>A101</t>
-  </si>
-  <si>
-    <t>A102</t>
-  </si>
-  <si>
-    <t>A103</t>
-  </si>
-  <si>
-    <t>A104</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>A105</t>
-  </si>
-  <si>
-    <t>A106</t>
-  </si>
-  <si>
-    <t>A107</t>
-  </si>
-  <si>
-    <t>A108</t>
-  </si>
-  <si>
-    <t>A109</t>
-  </si>
-  <si>
-    <t>A110</t>
-  </si>
-  <si>
-    <t>A111</t>
-  </si>
-  <si>
-    <t>A112</t>
-  </si>
-  <si>
-    <t>A113</t>
-  </si>
-  <si>
-    <t>A201</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>A202</t>
-  </si>
-  <si>
-    <t>A203</t>
-  </si>
-  <si>
-    <t>A204</t>
-  </si>
-  <si>
-    <t>A205</t>
-  </si>
-  <si>
-    <t>A206</t>
-  </si>
-  <si>
-    <t>A207</t>
-  </si>
-  <si>
-    <t>Air</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[false,false,false,true]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,0,0,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AirElementBottle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>气元素瓶</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicAirPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础气流药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AirPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>气流药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TailwindPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>顺风药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Draw,Damage_Windborne]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage_Windborne,Draw,Damage]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,1,2]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,1,3]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,1,3]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Draw,Damage_Self]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装沟壑</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledFissure</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Stun_Enemy,Damage,Draw]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,1,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,1,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1,6,0]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装沙暴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledSandstorm</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,5,5]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>基岩</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bedrock</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,8,1]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>热砂药剂</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage_Focus,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,6,3]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScorchingSandsPotion</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Buff_Sturdy_Self_Focus,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,7,5]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Elemental_Earth,Damage_Focus,Damage_Focus]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2,5,5]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1859,29 +1884,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2339,7 +2365,7 @@
         <v>45</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
         <v>39</v>
@@ -2397,10 +2423,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -2429,10 +2455,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -2460,7 +2486,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2523,7 +2549,7 @@
         <v>57</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -2558,7 +2584,7 @@
         <v>61</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2567,7 +2593,7 @@
         <v>33</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>58</v>
@@ -2579,7 +2605,7 @@
         <v>62</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>64</v>
@@ -2593,7 +2619,7 @@
         <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>39</v>
@@ -2628,7 +2654,7 @@
         <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>39</v>
@@ -2663,7 +2689,7 @@
         <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>39</v>
@@ -2698,7 +2724,7 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>39</v>
@@ -2733,7 +2759,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>39</v>
@@ -2768,7 +2794,7 @@
         <v>91</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -2803,7 +2829,7 @@
         <v>96</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>39</v>
@@ -2838,7 +2864,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>39</v>
@@ -2870,10 +2896,10 @@
         <v>106</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>39</v>
@@ -2905,10 +2931,10 @@
         <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>39</v>
@@ -2940,10 +2966,10 @@
         <v>114</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>39</v>
@@ -2975,10 +3001,10 @@
         <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>39</v>
@@ -3013,7 +3039,7 @@
         <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>39</v>
@@ -3048,7 +3074,7 @@
         <v>128</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>39</v>
@@ -3057,7 +3083,7 @@
         <v>67</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>58</v>
@@ -3068,22 +3094,22 @@
       <c r="J19" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>39</v>
@@ -3095,30 +3121,30 @@
         <v>40</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="L20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="C21" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>39</v>
@@ -3136,24 +3162,24 @@
         <v>9</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="L21" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>39</v>
@@ -3171,24 +3197,24 @@
         <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="L22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>39</v>
@@ -3206,24 +3232,24 @@
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="L23" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>39</v>
@@ -3241,17 +3267,17 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>154</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3309,13 +3335,13 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>51</v>
@@ -3327,7 +3353,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -3339,18 +3365,18 @@
         <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>51</v>
@@ -3362,106 +3388,106 @@
         <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
@@ -3473,71 +3499,71 @@
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I8" s="2">
         <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -3546,97 +3572,97 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
       </c>
       <c r="J11" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
@@ -3648,106 +3674,106 @@
         <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1">
       <c r="A14" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
@@ -3756,53 +3782,53 @@
         <v>34</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
@@ -3811,33 +3837,33 @@
         <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
@@ -3846,7 +3872,7 @@
         <v>51</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
@@ -3858,21 +3884,21 @@
         <v>8</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
@@ -3881,33 +3907,33 @@
         <v>51</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -3916,33 +3942,33 @@
         <v>51</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -3951,7 +3977,7 @@
         <v>51</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
@@ -3963,21 +3989,21 @@
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -3986,33 +4012,33 @@
         <v>51</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I23" s="3">
         <v>9</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -4021,25 +4047,25 @@
         <v>51</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4052,7 +4078,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4110,16 +4136,16 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -4128,7 +4154,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4137,24 +4163,24 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -4163,684 +4189,684 @@
         <v>46</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>358</v>
-      </c>
       <c r="G4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>358</v>
-      </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>391</v>
-      </c>
       <c r="L5" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>358</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K14" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>439</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>426</v>
+      <c r="H18" s="22" t="s">
+        <v>424</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>385</v>
+        <v>513</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>456</v>
+        <v>517</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4853,7 +4879,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4911,16 +4937,16 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -4929,7 +4955,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4938,24 +4964,24 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1">
       <c r="A3" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -4964,182 +4990,182 @@
         <v>46</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>478</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>480</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -5148,500 +5174,500 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1">
       <c r="A18" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1">
       <c r="A19" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1">
       <c r="A20" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1">
       <c r="A21" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1">
       <c r="A22" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1">
       <c r="A23" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1">
       <c r="A24" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5654,7 +5680,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5711,16 +5737,16 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -5729,27 +5755,27 @@
         <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I2" s="1">
         <v>4</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>32</v>
@@ -5758,33 +5784,33 @@
         <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I4" s="2">
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1">
       <c r="A5" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -5793,103 +5819,103 @@
         <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I5" s="2">
         <v>4</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I6" s="2">
         <v>4</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I7" s="2">
         <v>6</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -5898,33 +5924,33 @@
         <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I8" s="2">
         <v>6</v>
       </c>
       <c r="J8" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
@@ -5933,7 +5959,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
@@ -5945,21 +5971,21 @@
         <v>5</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1">
       <c r="A11" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>32</v>
@@ -5968,33 +5994,33 @@
         <v>51</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I11" s="3">
         <v>7</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1">
       <c r="A12" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>32</v>
@@ -6003,7 +6029,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>40</v>
@@ -6015,65 +6041,65 @@
         <v>7</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1">
       <c r="A13" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I13" s="3">
         <v>8</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1">
       <c r="A14" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>40</v>
@@ -6085,52 +6111,52 @@
         <v>7</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1">
       <c r="A15" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I15" s="3">
         <v>10</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>315</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E35D1-16C6-4B71-8D4C-E356ACD19DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E942BF-20DB-4AAD-92B8-920B612C38BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="527">
   <si>
     <t>Id</t>
   </si>
@@ -981,19 +981,19 @@
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>B01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>B02</t>
@@ -1003,167 +1003,167 @@
   </si>
   <si>
     <t>InternalBurningPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>UnstableFirePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EmberPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BottledFireball</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BottledPhoenix</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BasicWaterPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Test</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Earth</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,true,false]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>E100</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>E101</t>
@@ -1176,7 +1176,7 @@
   </si>
   <si>
     <t>E104</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>E105</t>
@@ -1207,7 +1207,7 @@
   </si>
   <si>
     <t>E201</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>E202</t>
@@ -1229,302 +1229,298 @@
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,2]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,3]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>待定占位</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>HealPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>NeutralizePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CyclePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CalmMindPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LamentOfTheWise</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,1,0]</t>
   </si>
   <si>
     <t>[0,0,1,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>健体药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,1,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[7,5,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[12,2,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,2,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,3,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[14,10,9]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Draw_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[5,8,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Reflect_Self,Draw,Damage]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[6,1,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Draw,Discard]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[9,2,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[3,0,3]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[6,5,6]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>A100</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>A101</t>
@@ -1537,7 +1533,7 @@
   </si>
   <si>
     <t>A104</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>A105</t>
@@ -1568,7 +1564,7 @@
   </si>
   <si>
     <t>A201</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>A202</t>
@@ -1590,183 +1586,230 @@
   </si>
   <si>
     <t>Air</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,false,true]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AirElementBottle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>气元素瓶</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BasicAirPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>基础气流药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AirPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>气流药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TailwindPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>顺风药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Draw,Damage_Windborne]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage_Windborne,Draw,Damage]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[5,1,2]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[4,1,3]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[0,1,3]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Draw,Damage_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沟壑</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BottledFissure</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Stun_Enemy,Damage,Draw]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[3,1,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沙暴</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BottledSandstorm</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[5,5,5]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>基岩</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Bedrock</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[5,8,1]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>热砂药剂</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[6,6,3]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ScorchingSandsPotion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self_Focus,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,7,5]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[3,2,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[7,1,0]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Damage,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[16,7,6]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Elemental_Fire,Buff_Burn_Self]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[Elemental_Earth,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>[2,5,5]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>和风药剂</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Heal,Damage_Self,Damage]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,3,0]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>强风药剂</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreezePotion</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrongWindPotion</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Quickness_Self,Damage_Self]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,1,6]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7,7,5]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,6,2]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,5,1]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1884,33 +1927,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2184,20 +2228,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.09765625" customWidth="1"/>
-    <col min="2" max="2" width="19.3984375" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="5" max="5" width="22.19921875" customWidth="1"/>
-    <col min="6" max="6" width="22.3984375" customWidth="1"/>
-    <col min="7" max="7" width="19.09765625" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="10" max="10" width="14.09765625" customWidth="1"/>
-    <col min="11" max="11" width="62.796875" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="62.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2232,7 +2276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2267,7 +2311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2302,7 +2346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2322,7 +2366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -2357,7 +2401,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2389,7 +2433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2421,7 +2465,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>316</v>
       </c>
@@ -2453,7 +2497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>318</v>
       </c>
@@ -2486,7 +2530,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2494,19 +2538,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2541,7 +2585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -2576,7 +2620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>60</v>
       </c>
@@ -2605,13 +2649,13 @@
         <v>62</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -2646,7 +2690,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -2681,7 +2725,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
@@ -2716,7 +2760,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -2751,7 +2795,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>85</v>
       </c>
@@ -2786,7 +2830,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>90</v>
       </c>
@@ -2821,7 +2865,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>95</v>
       </c>
@@ -2856,7 +2900,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
@@ -2891,7 +2935,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>106</v>
       </c>
@@ -2926,7 +2970,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
@@ -2961,7 +3005,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
@@ -2996,7 +3040,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>118</v>
       </c>
@@ -3031,7 +3075,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>122</v>
       </c>
@@ -3066,7 +3110,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>127</v>
       </c>
@@ -3095,13 +3139,13 @@
         <v>129</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>131</v>
       </c>
@@ -3136,7 +3180,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>137</v>
       </c>
@@ -3171,7 +3215,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>142</v>
       </c>
@@ -3206,7 +3250,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>146</v>
       </c>
@@ -3241,7 +3285,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>150</v>
       </c>
@@ -3267,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>151</v>
@@ -3277,7 +3321,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3285,20 +3329,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="3" width="28.296875" customWidth="1"/>
-    <col min="4" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3333,7 +3377,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>153</v>
       </c>
@@ -3368,7 +3412,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>157</v>
       </c>
@@ -3403,7 +3447,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>161</v>
       </c>
@@ -3438,7 +3482,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>167</v>
       </c>
@@ -3473,7 +3517,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>172</v>
       </c>
@@ -3508,7 +3552,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>176</v>
       </c>
@@ -3543,7 +3587,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>180</v>
       </c>
@@ -3578,7 +3622,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>183</v>
       </c>
@@ -3613,7 +3657,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>187</v>
       </c>
@@ -3648,7 +3692,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>193</v>
       </c>
@@ -3683,7 +3727,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>198</v>
       </c>
@@ -3718,7 +3762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>203</v>
       </c>
@@ -3753,7 +3797,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>207</v>
       </c>
@@ -3788,7 +3832,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>211</v>
       </c>
@@ -3823,7 +3867,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>216</v>
       </c>
@@ -3858,7 +3902,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>220</v>
       </c>
@@ -3893,7 +3937,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>225</v>
       </c>
@@ -3928,7 +3972,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>230</v>
       </c>
@@ -3963,7 +4007,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>235</v>
       </c>
@@ -3998,7 +4042,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>240</v>
       </c>
@@ -4033,7 +4077,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>246</v>
       </c>
@@ -4068,17 +4112,17 @@
         <v>250</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4086,20 +4130,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2441ED13-5DB1-49F6-B610-4785970FA9EB}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="3" width="28.296875" customWidth="1"/>
-    <col min="4" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4134,7 +4178,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>360</v>
       </c>
@@ -4163,13 +4207,13 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>361</v>
       </c>
@@ -4195,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>383</v>
@@ -4204,7 +4248,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>362</v>
       </c>
@@ -4239,7 +4283,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>363</v>
       </c>
@@ -4274,7 +4318,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>364</v>
       </c>
@@ -4300,7 +4344,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>403</v>
@@ -4309,12 +4353,12 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>365</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -4335,21 +4379,21 @@
         <v>5</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>366</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
@@ -4370,21 +4414,21 @@
         <v>5</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K9" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>367</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
@@ -4405,21 +4449,21 @@
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>368</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
@@ -4434,27 +4478,27 @@
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>369</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -4469,27 +4513,27 @@
         <v>46</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>370</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
@@ -4510,21 +4554,21 @@
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K13" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>371</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
@@ -4539,27 +4583,27 @@
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="K14" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>372</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
@@ -4580,21 +4624,21 @@
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>373</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
@@ -4609,22 +4653,22 @@
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>374</v>
       </c>
@@ -4644,27 +4688,27 @@
         <v>40</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>375</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
@@ -4679,27 +4723,27 @@
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
-      <c r="J19" s="14" t="s">
-        <v>384</v>
+      <c r="J19" s="6" t="s">
+        <v>525</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>376</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
@@ -4714,27 +4758,27 @@
         <v>40</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>377</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -4749,27 +4793,27 @@
         <v>40</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>378</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -4784,27 +4828,27 @@
         <v>40</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>379</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -4825,21 +4869,21 @@
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>380</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -4860,26 +4904,26 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4887,20 +4931,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C02A9BF-5C11-492C-BF77-FB0B6AF52D8A}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="3" width="28.296875" customWidth="1"/>
-    <col min="4" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4935,18 +4979,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -4955,7 +4999,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4964,24 +5008,24 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
-      <c r="A3" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -4990,176 +5034,176 @@
         <v>46</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L3" s="7" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
-      <c r="A4" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>477</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>478</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L4" s="7" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>484</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
-      <c r="A5" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>485</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>477</v>
-      </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>492</v>
-      </c>
       <c r="L5" s="7" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>402</v>
+        <v>458</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>520</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>354</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>400</v>
+      <c r="H7" s="23" t="s">
+        <v>443</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>403</v>
+      <c r="J7" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>517</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>408</v>
+        <v>459</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>521</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>400</v>
+      <c r="H8" s="23" t="s">
+        <v>443</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>409</v>
+      <c r="J8" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>522</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
@@ -5174,27 +5218,27 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
@@ -5206,100 +5250,100 @@
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
@@ -5311,65 +5355,65 @@
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
@@ -5381,53 +5425,53 @@
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>401</v>
@@ -5436,22 +5480,22 @@
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>383</v>
@@ -5460,27 +5504,27 @@
         <v>388</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
@@ -5489,50 +5533,50 @@
         <v>384</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>231</v>
@@ -5541,10 +5585,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
@@ -5565,9 +5609,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>236</v>
@@ -5576,10 +5620,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
@@ -5600,9 +5644,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>241</v>
@@ -5611,10 +5655,10 @@
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
@@ -5635,9 +5679,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>247</v>
@@ -5646,10 +5690,10 @@
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
@@ -5670,17 +5714,17 @@
         <v>388</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5688,19 +5732,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
-    <col min="3" max="4" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" customWidth="1"/>
-    <col min="11" max="11" width="45.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5735,7 +5779,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>251</v>
       </c>
@@ -5770,7 +5814,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1">
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>258</v>
       </c>
@@ -5805,7 +5849,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1">
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>264</v>
       </c>
@@ -5840,7 +5884,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1">
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>269</v>
       </c>
@@ -5875,7 +5919,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>274</v>
       </c>
@@ -5910,7 +5954,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>278</v>
       </c>
@@ -5945,7 +5989,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>283</v>
       </c>
@@ -5980,7 +6024,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1">
+    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>288</v>
       </c>
@@ -6015,7 +6059,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1">
+    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>293</v>
       </c>
@@ -6050,7 +6094,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1">
+    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>298</v>
       </c>
@@ -6085,7 +6129,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1">
+    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>304</v>
       </c>
@@ -6120,7 +6164,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1">
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>309</v>
       </c>
@@ -6156,7 +6200,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E942BF-20DB-4AAD-92B8-920B612C38BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4DD780-BC75-45AA-B3B8-4AEB16353E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="552">
   <si>
     <t>Id</t>
   </si>
@@ -981,19 +981,19 @@
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>B01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>B02</t>
@@ -1003,167 +1003,167 @@
   </si>
   <si>
     <t>InternalBurningPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>UnstableFirePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>EmberPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>ExternalBurningPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BottledFireball</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BottledPhoenix</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BottledSimianSpirit</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FireElementBottle</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BasicFirePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FirePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PowerPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.HeatTherapy</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.CatalyzePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ScalePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.FlashPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.WillOWisp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BlastPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.InternalBurningPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.UnstableFirePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.EmberPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.ExternalBurningPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.GreaterFirePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.PulsePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.SuperNova</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.MidasPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledFireball</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledPhoenix</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Fire/Card.BottledSimianSpirit</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterElementBottle</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BasicWaterPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.BasicWaterPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.WaterPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.SpeedPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Test</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Earth</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,true,false]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>E100</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>E101</t>
@@ -1176,7 +1176,7 @@
   </si>
   <si>
     <t>E104</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>E105</t>
@@ -1207,7 +1207,7 @@
   </si>
   <si>
     <t>E201</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>E202</t>
@@ -1229,298 +1229,266 @@
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,3,2]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,3,3]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>待定占位</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Draw_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>HealPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.HealPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>NeutralizePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.NeutralizePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>CyclePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>CalmMindPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.CalmMindPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>LamentOfTheWise</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Card/Water/Card.LamentOfTheWise</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,1,0]</t>
   </si>
   <si>
     <t>[0,0,1,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>健体药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self,Buff_Sturdy_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[7,5,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Stun_Enemy,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Draw,Buff_Reflect_Self,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1,6,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Heal,Draw_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[12,2,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,2,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,3,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[4,3,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[14,10,9]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Draw_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,8,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Reflect_Self,Draw,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[6,1,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Buff_Sturdy_Self_Focus,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[3,3,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Draw,Discard]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[9,2,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Sturdy_Self_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[3,0,3]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,5,6]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>A100</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>A101</t>
@@ -1533,7 +1501,7 @@
   </si>
   <si>
     <t>A104</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>A105</t>
@@ -1564,7 +1532,7 @@
   </si>
   <si>
     <t>A201</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>A202</t>
@@ -1586,223 +1554,369 @@
   </si>
   <si>
     <t>Air</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[false,false,false,true]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,0,0,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AirElementBottle</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>气元素瓶</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BasicAirPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>基础气流药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AirPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>气流药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>TailwindPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>顺风药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage,Draw,Damage_Windborne]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Damage_Windborne,Draw,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,1,2]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,1,3]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[0,1,3]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Draw,Damage_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沟壑</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BottledFissure</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Stun_Enemy,Damage,Draw]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,1,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[1,6,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沙暴</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BottledSandstorm</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[5,5,5]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>基岩</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Bedrock</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,8,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>热砂药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Damage_Focus,Buff_Burn_Enemy]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[6,6,3]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>ScorchingSandsPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self_Focus,Buff_Sturdy_Self,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[3,2,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[7,1,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Buff_Sturdy_Self,Damage,Buff_Reflect_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[16,7,6]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Draw,Elemental_Fire,Buff_Burn_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Elemental_Earth,Damage_Focus,Damage_Focus]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[2,5,5]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>和风药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Heal,Damage_Self,Damage]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,3,0]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>强风药剂</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BreezePotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>StrongWindPotion</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[Damage,Buff_Quickness_Self,Damage_Self]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[4,1,6]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[7,7,5]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>[4,6,2]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3,5,1]</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,2,3]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,3,4]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,1,3]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,4,3]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,1,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,4,4]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7,2,1]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵风药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>GustPotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,0]</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Draw,Discard,Draw]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>TornadoPotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage_Self,Damage,Damage_Self]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2,7,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,1,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,3,1]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterAirPotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等气流药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Quickness_Self,Damage_Windborne]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,2,4]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HurricanePotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>飓风药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage_Self,Discard,Damage_Windborne]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2,3,9]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConvectionPotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>对流药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,1,1]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>SevereConvectionPotion</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>强对流药剂</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,3]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Elemental_Air,Draw,Discard]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Elemental_Air,Draw,Damage_Self]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Draw,Damage_Aftermath]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3,1,4]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage,Buff_Quickness_Self,Damage_Aftermath]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false,false,false]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>FairyWind</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖精之风</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Damage_Aftermath,Draw_Aftermath,Heal_Aftermath]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,1,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1881,11 +1995,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1927,30 +2045,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2530,7 +2650,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2649,7 +2769,7 @@
         <v>62</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>64</v>
@@ -3138,8 +3258,8 @@
       <c r="J19" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K19" s="22" t="s">
-        <v>513</v>
+      <c r="K19" s="21" t="s">
+        <v>499</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>130</v>
@@ -3311,7 +3431,7 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>151</v>
@@ -3321,7 +3441,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3522,10 +3642,10 @@
         <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
@@ -3557,10 +3677,10 @@
         <v>176</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>51</v>
@@ -3592,10 +3712,10 @@
         <v>180</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>51</v>
@@ -3627,10 +3747,10 @@
         <v>183</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>51</v>
@@ -3665,7 +3785,7 @@
         <v>188</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>51</v>
@@ -3700,7 +3820,7 @@
         <v>194</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>51</v>
@@ -3735,7 +3855,7 @@
         <v>199</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>51</v>
@@ -3767,10 +3887,10 @@
         <v>203</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>51</v>
@@ -3805,7 +3925,7 @@
         <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>51</v>
@@ -3840,7 +3960,7 @@
         <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>51</v>
@@ -4122,7 +4242,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4198,7 +4318,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -4207,7 +4327,7 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>357</v>
@@ -4233,13 +4353,13 @@
         <v>46</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>383</v>
@@ -4268,13 +4388,13 @@
         <v>46</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>384</v>
+        <v>511</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>383</v>
@@ -4288,7 +4408,7 @@
         <v>363</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>354</v>
@@ -4303,19 +4423,19 @@
         <v>46</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>389</v>
-      </c>
       <c r="L5" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4323,7 +4443,7 @@
         <v>364</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>354</v>
@@ -4338,19 +4458,19 @@
         <v>46</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4358,7 +4478,7 @@
         <v>365</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -4373,19 +4493,19 @@
         <v>46</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4393,7 +4513,7 @@
         <v>366</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
@@ -4408,19 +4528,19 @@
         <v>46</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>495</v>
+      <c r="J9" s="23" t="s">
+        <v>512</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4428,7 +4548,7 @@
         <v>367</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
@@ -4443,19 +4563,19 @@
         <v>46</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>417</v>
+        <v>514</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4463,7 +4583,7 @@
         <v>368</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
@@ -4478,19 +4598,19 @@
         <v>46</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4498,7 +4618,7 @@
         <v>369</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -4512,20 +4632,20 @@
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>422</v>
+      <c r="H12" s="23" t="s">
+        <v>398</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>502</v>
+      <c r="J12" s="5" t="s">
+        <v>513</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4533,7 +4653,7 @@
         <v>370</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
@@ -4548,19 +4668,19 @@
         <v>46</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>433</v>
+        <v>514</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4568,7 +4688,7 @@
         <v>371</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
@@ -4583,19 +4703,19 @@
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -4603,7 +4723,7 @@
         <v>372</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
@@ -4618,19 +4738,19 @@
         <v>46</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>441</v>
+        <v>516</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4638,7 +4758,7 @@
         <v>373</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
@@ -4653,19 +4773,19 @@
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4673,7 +4793,7 @@
         <v>374</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
@@ -4687,20 +4807,20 @@
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>423</v>
+      <c r="H18" s="21" t="s">
+        <v>419</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4708,7 +4828,7 @@
         <v>375</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
@@ -4723,19 +4843,19 @@
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4743,7 +4863,7 @@
         <v>376</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
@@ -4758,19 +4878,19 @@
         <v>40</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4778,7 +4898,7 @@
         <v>377</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -4793,19 +4913,19 @@
         <v>40</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4813,7 +4933,7 @@
         <v>378</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -4828,19 +4948,19 @@
         <v>40</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4848,7 +4968,7 @@
         <v>379</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -4863,19 +4983,19 @@
         <v>40</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4883,7 +5003,7 @@
         <v>380</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -4898,19 +5018,19 @@
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -4923,7 +5043,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4981,16 +5101,16 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -4999,7 +5119,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -5008,24 +5128,24 @@
         <v>34</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -5034,182 +5154,182 @@
         <v>46</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>486</v>
+        <v>546</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>520</v>
+        <v>450</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>505</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>354</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>443</v>
+      <c r="H7" s="22" t="s">
+        <v>437</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>443</v>
+      <c r="H8" s="22" t="s">
+        <v>437</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>413</v>
+        <v>452</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>518</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>399</v>
+      <c r="H9" s="23" t="s">
+        <v>519</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -5218,365 +5338,365 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>411</v>
+        <v>520</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>388</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>415</v>
+        <v>453</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>521</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>399</v>
+      <c r="H10" s="23" t="s">
+        <v>519</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>417</v>
+        <v>524</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>416</v>
+        <v>523</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>388</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>418</v>
+        <v>454</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>531</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>422</v>
+      <c r="H11" s="25" t="s">
+        <v>437</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>420</v>
+        <v>534</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>388</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>427</v>
+        <v>455</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>535</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>422</v>
+      <c r="H12" s="25" t="s">
+        <v>537</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>428</v>
+      <c r="J12" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>542</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>388</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>401</v>
+        <v>460</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>527</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>423</v>
+      <c r="H18" s="24" t="s">
+        <v>469</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>383</v>
+      <c r="J18" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>529</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>388</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>448</v>
+        <v>461</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>539</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>443</v>
+      <c r="H19" s="24" t="s">
+        <v>541</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
-      <c r="J19" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>449</v>
+      <c r="J19" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>543</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>388</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>450</v>
+        <v>462</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>548</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="17" t="s">
-        <v>422</v>
+      <c r="H20" s="24" t="s">
+        <v>469</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
-      <c r="J20" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>452</v>
+      <c r="J20" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>550</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>388</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>231</v>
@@ -5585,16 +5705,16 @@
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I21" s="3">
         <v>8</v>
@@ -5606,12 +5726,12 @@
         <v>233</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>236</v>
@@ -5620,16 +5740,16 @@
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I22" s="3">
         <v>8</v>
@@ -5641,12 +5761,12 @@
         <v>238</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>241</v>
@@ -5655,16 +5775,16 @@
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I23" s="3">
         <v>8</v>
@@ -5676,12 +5796,12 @@
         <v>244</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>247</v>
@@ -5690,16 +5810,16 @@
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I24" s="3">
         <v>8</v>
@@ -5711,7 +5831,7 @@
         <v>249</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -5724,7 +5844,7 @@
       <c r="K28" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6200,7 +6320,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/Assets/Game/Content/Data/CardTable.xlsx
+++ b/Assets/Game/Content/Data/CardTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4DD780-BC75-45AA-B3B8-4AEB16353E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BD8662-000E-4F36-93DF-76D02F9947D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="555">
   <si>
     <t>Id</t>
   </si>
@@ -1408,10 +1408,6 @@
   </si>
   <si>
     <t>SpikePotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>[6,1,1]</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1890,6 +1886,22 @@
   </si>
   <si>
     <t>[1,1,2]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReactiveGas</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>活性气体</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,1]</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Catalyze,Neutralize,Catalyze]</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2769,7 +2781,7 @@
         <v>62</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>64</v>
@@ -3259,7 +3271,7 @@
         <v>129</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>130</v>
@@ -3431,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>151</v>
@@ -4394,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>383</v>
@@ -4429,7 +4441,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>387</v>
@@ -4464,7 +4476,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>401</v>
@@ -4534,7 +4546,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>409</v>
@@ -4569,7 +4581,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>424</v>
@@ -4639,7 +4651,7 @@
         <v>5</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>423</v>
@@ -4674,7 +4686,7 @@
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>424</v>
@@ -4688,7 +4700,7 @@
         <v>371</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
@@ -4709,13 +4721,13 @@
         <v>5</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -4723,7 +4735,7 @@
         <v>372</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
@@ -4744,13 +4756,13 @@
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4758,7 +4770,7 @@
         <v>373</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
@@ -4773,19 +4785,19 @@
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4814,10 +4826,10 @@
         <v>8</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>403</v>
@@ -4828,7 +4840,7 @@
         <v>375</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
@@ -4843,19 +4855,19 @@
         <v>40</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4863,7 +4875,7 @@
         <v>376</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
@@ -4884,13 +4896,13 @@
         <v>8</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4898,7 +4910,7 @@
         <v>377</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
@@ -4919,13 +4931,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4933,7 +4945,7 @@
         <v>378</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -4954,13 +4966,13 @@
         <v>8</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>408</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4968,7 +4980,7 @@
         <v>379</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
@@ -4989,13 +5001,13 @@
         <v>8</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5003,7 +5015,7 @@
         <v>380</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>32</v>
@@ -5024,13 +5036,13 @@
         <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -5101,16 +5113,16 @@
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -5119,7 +5131,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -5131,21 +5143,21 @@
         <v>408</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -5154,182 +5166,182 @@
         <v>46</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>468</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>469</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>546</v>
-      </c>
       <c r="L4" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>354</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>468</v>
-      </c>
       <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>479</v>
-      </c>
       <c r="L5" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>354</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -5338,167 +5350,167 @@
         <v>52</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>426</v>
+        <v>455</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>551</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>547</v>
-      </c>
       <c r="G13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>397</v>
+      <c r="H13" s="25" t="s">
+        <v>553</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>427</v>
+        <v>544</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>424</v>
+        <v>554</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>386</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>46</v>
@@ -5510,10 +5522,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>386</v>
@@ -5521,19 +5533,19 @@
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>46</v>
@@ -5545,10 +5557,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>386</v>
@@ -5556,34 +5568,34 @@
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>386</v>
@@ -5591,112 +5603,112 @@
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I18" s="3">
         <v>8</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I19" s="3">
         <v>8</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I20" s="3">
         <v>8</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>231</v>
@@ -5705,10 +5717,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>40</v>
@@ -5731,7 +5743,7 @@
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>236</v>
@@ -5740,10 +5752,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>40</v>
@@ -5766,7 +5778,7 @@
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>241</v>
@@ -5775,10 +5787,10 @@
         <v>32</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>40</v>
@@ -5801,7 +5813,7 @@
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>247</v>
@@ -5810,10 +5822,10 @@
         <v>32</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>40</v>
